--- a/Geerts 2023 Figure 4B.xlsx
+++ b/Geerts 2023 Figure 4B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elber\Documents\git\JSON2SBML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E4B88F-0D93-4E3E-861A-454AC984D73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6490C153-1581-4167-8B7E-29D88E17A6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{11BF9699-13C9-414D-89A9-59116B7674A8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="12">
   <si>
     <t>Time (h)</t>
   </si>
@@ -63,6 +63,15 @@
   </si>
   <si>
     <t>sim10mgkg</t>
+  </si>
+  <si>
+    <t>sim3mgkg</t>
+  </si>
+  <si>
+    <t>sim1mgkg</t>
+  </si>
+  <si>
+    <t>sim0p1mgkg</t>
   </si>
 </sst>
 </file>
@@ -434,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B1C395F-71E4-42DA-AD74-5388AF7594A9}">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
@@ -471,11 +480,11 @@
         <v>2313.5083727440401</v>
       </c>
       <c r="E2">
-        <f>C2/24/365+70</f>
+        <f t="shared" ref="E2:E33" si="0">C2/24/365+70</f>
         <v>70.000065753719099</v>
       </c>
       <c r="F2">
-        <f>D2</f>
+        <f t="shared" ref="F2:F33" si="1">D2</f>
         <v>2313.5083727440401</v>
       </c>
     </row>
@@ -493,11 +502,11 @@
         <v>2032.09737342624</v>
       </c>
       <c r="E3">
-        <f>C3/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.001122838535821</v>
       </c>
       <c r="F3">
-        <f>D3</f>
+        <f t="shared" si="1"/>
         <v>2032.09737342624</v>
       </c>
     </row>
@@ -515,11 +524,11 @@
         <v>1764.8536649039199</v>
       </c>
       <c r="E4">
-        <f>C4/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.002245677071642</v>
       </c>
       <c r="F4">
-        <f>D4</f>
+        <f t="shared" si="1"/>
         <v>1764.8536649039199</v>
       </c>
     </row>
@@ -537,11 +546,11 @@
         <v>1644.9065721603999</v>
       </c>
       <c r="E5">
-        <f>C5/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.002994236095518</v>
       </c>
       <c r="F5">
-        <f>D5</f>
+        <f t="shared" si="1"/>
         <v>1644.9065721603999</v>
       </c>
     </row>
@@ -559,11 +568,11 @@
         <v>1523.4689898513</v>
       </c>
       <c r="E6">
-        <f>C6/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.003561954697119</v>
       </c>
       <c r="F6">
-        <f>D6</f>
+        <f t="shared" si="1"/>
         <v>1523.4689898513</v>
       </c>
     </row>
@@ -581,11 +590,11 @@
         <v>1365.9320024210899</v>
       </c>
       <c r="E7">
-        <f>C7/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.004650394624235</v>
       </c>
       <c r="F7">
-        <f>D7</f>
+        <f t="shared" si="1"/>
         <v>1365.9320024210899</v>
       </c>
     </row>
@@ -603,11 +612,11 @@
         <v>1246.77854072632</v>
       </c>
       <c r="E8">
-        <f>C8/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.005738834551352</v>
       </c>
       <c r="F8">
-        <f>D8</f>
+        <f t="shared" si="1"/>
         <v>1246.77854072632</v>
       </c>
     </row>
@@ -625,11 +634,11 @@
         <v>1144.8216031076299</v>
       </c>
       <c r="E9">
-        <f>C9/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.006827274478468</v>
       </c>
       <c r="F9">
-        <f>D9</f>
+        <f t="shared" si="1"/>
         <v>1144.8216031076299</v>
       </c>
     </row>
@@ -647,11 +656,11 @@
         <v>1064.71306343323</v>
       </c>
       <c r="E10">
-        <f>C10/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.007915714405598</v>
       </c>
       <c r="F10">
-        <f>D10</f>
+        <f t="shared" si="1"/>
         <v>1064.71306343323</v>
       </c>
     </row>
@@ -669,11 +678,11 @@
         <v>996.97750518580096</v>
       </c>
       <c r="E11">
-        <f>C11/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.009004154332715</v>
       </c>
       <c r="F11">
-        <f>D11</f>
+        <f t="shared" si="1"/>
         <v>996.97750518580096</v>
       </c>
     </row>
@@ -691,11 +700,11 @@
         <v>939.93137456029797</v>
       </c>
       <c r="E12">
-        <f>C12/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.010092594259831</v>
       </c>
       <c r="F12">
-        <f>D12</f>
+        <f t="shared" si="1"/>
         <v>939.93137456029797</v>
       </c>
     </row>
@@ -713,11 +722,11 @@
         <v>895.76641104979399</v>
       </c>
       <c r="E13">
-        <f>C13/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.01115134946167</v>
       </c>
       <c r="F13">
-        <f>D13</f>
+        <f t="shared" si="1"/>
         <v>895.76641104979399</v>
       </c>
     </row>
@@ -735,11 +744,11 @@
         <v>851.96548287923099</v>
       </c>
       <c r="E14">
-        <f>C14/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.012269474114063</v>
       </c>
       <c r="F14">
-        <f>D14</f>
+        <f t="shared" si="1"/>
         <v>851.96548287923099</v>
       </c>
     </row>
@@ -757,11 +766,11 @@
         <v>814.23320128383295</v>
       </c>
       <c r="E15">
-        <f>C15/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.013357914041194</v>
       </c>
       <c r="F15">
-        <f>D15</f>
+        <f t="shared" si="1"/>
         <v>814.23320128383295</v>
       </c>
     </row>
@@ -779,11 +788,11 @@
         <v>784.57607411433696</v>
       </c>
       <c r="E16">
-        <f>C16/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.014391382254814</v>
       </c>
       <c r="F16">
-        <f>D16</f>
+        <f t="shared" si="1"/>
         <v>784.57607411433696</v>
       </c>
     </row>
@@ -801,11 +810,11 @@
         <v>751.98501909245294</v>
       </c>
       <c r="E17">
-        <f>C17/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.015534793895426</v>
       </c>
       <c r="F17">
-        <f>D17</f>
+        <f t="shared" si="1"/>
         <v>751.98501909245294</v>
       </c>
     </row>
@@ -823,11 +832,11 @@
         <v>724.43900448117995</v>
       </c>
       <c r="E18">
-        <f>C18/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.016678205536039</v>
       </c>
       <c r="F18">
-        <f>D18</f>
+        <f t="shared" si="1"/>
         <v>724.43900448117995</v>
       </c>
     </row>
@@ -845,11 +854,11 @@
         <v>701.62747233454797</v>
       </c>
       <c r="E19">
-        <f>C19/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.017711673749659</v>
       </c>
       <c r="F19">
-        <f>D19</f>
+        <f t="shared" si="1"/>
         <v>701.62747233454797</v>
       </c>
     </row>
@@ -867,11 +876,11 @@
         <v>676.86281695751904</v>
       </c>
       <c r="E20">
-        <f>C20/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.018800113676789</v>
       </c>
       <c r="F20">
-        <f>D20</f>
+        <f t="shared" si="1"/>
         <v>676.86281695751904</v>
       </c>
     </row>
@@ -889,11 +898,11 @@
         <v>654.64217695278603</v>
       </c>
       <c r="E21">
-        <f>C21/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.019888553603906</v>
       </c>
       <c r="F21">
-        <f>D21</f>
+        <f t="shared" si="1"/>
         <v>654.64217695278603</v>
       </c>
     </row>
@@ -911,11 +920,11 @@
         <v>635.31090913116304</v>
       </c>
       <c r="E22">
-        <f>C22/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.020976993531022</v>
       </c>
       <c r="F22">
-        <f>D22</f>
+        <f t="shared" si="1"/>
         <v>635.31090913116304</v>
       </c>
     </row>
@@ -933,11 +942,11 @@
         <v>617.74760455393903</v>
       </c>
       <c r="E23">
-        <f>C23/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.022035748732861</v>
       </c>
       <c r="F23">
-        <f>D23</f>
+        <f t="shared" si="1"/>
         <v>617.74760455393903</v>
       </c>
     </row>
@@ -955,11 +964,11 @@
         <v>594.78870778744601</v>
       </c>
       <c r="E24">
-        <f>C24/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.023153873385255</v>
       </c>
       <c r="F24">
-        <f>D24</f>
+        <f t="shared" si="1"/>
         <v>594.78870778744601</v>
       </c>
     </row>
@@ -977,11 +986,11 @@
         <v>579.68732104543096</v>
       </c>
       <c r="E25">
-        <f>C25/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.024242313312385</v>
       </c>
       <c r="F25">
-        <f>D25</f>
+        <f t="shared" si="1"/>
         <v>579.68732104543096</v>
       </c>
     </row>
@@ -999,11 +1008,11 @@
         <v>559.70298660376397</v>
       </c>
       <c r="E26">
-        <f>C26/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.025330753239501</v>
       </c>
       <c r="F26">
-        <f>D26</f>
+        <f t="shared" si="1"/>
         <v>559.70298660376397</v>
       </c>
     </row>
@@ -1021,11 +1030,11 @@
         <v>546.29258151498505</v>
       </c>
       <c r="E27">
-        <f>C27/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.026342232767732</v>
       </c>
       <c r="F27">
-        <f>D27</f>
+        <f t="shared" si="1"/>
         <v>546.29258151498505</v>
       </c>
     </row>
@@ -1043,11 +1052,11 @@
         <v>527.13552474737503</v>
       </c>
       <c r="E28">
-        <f>C28/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.027507633093734</v>
       </c>
       <c r="F28">
-        <f>D28</f>
+        <f t="shared" si="1"/>
         <v>527.13552474737503</v>
       </c>
     </row>
@@ -1065,11 +1074,11 @@
         <v>519.98970806881698</v>
       </c>
       <c r="E29">
-        <f>C29/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.028150802141582</v>
       </c>
       <c r="F29">
-        <f>D29</f>
+        <f t="shared" si="1"/>
         <v>519.98970806881698</v>
       </c>
     </row>
@@ -1087,11 +1096,11 @@
         <v>71.322641881135894</v>
       </c>
       <c r="E30">
-        <f>C30/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.031069800127952</v>
       </c>
       <c r="F30">
-        <f>D30</f>
+        <f t="shared" si="1"/>
         <v>71.322641881135894</v>
       </c>
     </row>
@@ -1109,11 +1118,11 @@
         <v>254.452981018245</v>
       </c>
       <c r="E31">
-        <f>C31/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.053828089513161</v>
       </c>
       <c r="F31">
-        <f>D31</f>
+        <f t="shared" si="1"/>
         <v>254.452981018245</v>
       </c>
     </row>
@@ -1131,11 +1140,11 @@
         <v>240.914536247755</v>
       </c>
       <c r="E32">
-        <f>C32/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.056044549001115</v>
       </c>
       <c r="F32">
-        <f>D32</f>
+        <f t="shared" si="1"/>
         <v>240.914536247755</v>
       </c>
     </row>
@@ -1153,11 +1162,11 @@
         <v>234.385416275121</v>
       </c>
       <c r="E33">
-        <f>C33/24/365+70</f>
+        <f t="shared" si="0"/>
         <v>70.057043934752386</v>
       </c>
       <c r="F33">
-        <f>D33</f>
+        <f t="shared" si="1"/>
         <v>234.385416275121</v>
       </c>
     </row>
@@ -1175,11 +1184,11 @@
         <v>226.22965796484499</v>
       </c>
       <c r="E34">
-        <f>C34/24/365+70</f>
+        <f t="shared" ref="E34:E65" si="2">C34/24/365+70</f>
         <v>70.05828079830593</v>
       </c>
       <c r="F34">
-        <f>D34</f>
+        <f t="shared" ref="F34:F65" si="3">D34</f>
         <v>226.22965796484499</v>
       </c>
     </row>
@@ -1197,11 +1206,11 @@
         <v>220.29816235619799</v>
       </c>
       <c r="E35">
-        <f>C35/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.059369238233046</v>
       </c>
       <c r="F35">
-        <f>D35</f>
+        <f t="shared" si="3"/>
         <v>220.29816235619799</v>
       </c>
     </row>
@@ -1219,11 +1228,11 @@
         <v>212.49154973856801</v>
       </c>
       <c r="E36">
-        <f>C36/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.06049725779387</v>
       </c>
       <c r="F36">
-        <f>D36</f>
+        <f t="shared" si="3"/>
         <v>212.49154973856801</v>
       </c>
     </row>
@@ -1241,11 +1250,11 @@
         <v>207.70305130892299</v>
       </c>
       <c r="E37">
-        <f>C37/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.061496643545141</v>
       </c>
       <c r="F37">
-        <f>D37</f>
+        <f t="shared" si="3"/>
         <v>207.70305130892299</v>
       </c>
     </row>
@@ -1263,11 +1272,11 @@
         <v>200.18104311900001</v>
       </c>
       <c r="E38">
-        <f>C38/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.062832456182974</v>
       </c>
       <c r="F38">
-        <f>D38</f>
+        <f t="shared" si="3"/>
         <v>200.18104311900001</v>
       </c>
     </row>
@@ -1285,11 +1294,11 @@
         <v>194.662566192155</v>
       </c>
       <c r="E39">
-        <f>C39/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.063821947025801</v>
       </c>
       <c r="F39">
-        <f>D39</f>
+        <f t="shared" si="3"/>
         <v>194.662566192155</v>
       </c>
     </row>
@@ -1307,11 +1316,11 @@
         <v>187.89213605559701</v>
       </c>
       <c r="E40">
-        <f>C40/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.065009336037207</v>
       </c>
       <c r="F40">
-        <f>D40</f>
+        <f t="shared" si="3"/>
         <v>187.89213605559701</v>
       </c>
     </row>
@@ -1329,11 +1338,11 @@
         <v>183.72505465504901</v>
       </c>
       <c r="E41">
-        <f>C41/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.066048301422185</v>
       </c>
       <c r="F41">
-        <f>D41</f>
+        <f t="shared" si="3"/>
         <v>183.72505465504901</v>
       </c>
     </row>
@@ -1351,11 +1360,11 @@
         <v>176.669033286001</v>
       </c>
       <c r="E42">
-        <f>C42/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.067285164975729</v>
       </c>
       <c r="F42">
-        <f>D42</f>
+        <f t="shared" si="3"/>
         <v>176.669033286001</v>
       </c>
     </row>
@@ -1373,11 +1382,11 @@
         <v>171.665907882683</v>
       </c>
       <c r="E43">
-        <f>C43/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.068324130360708</v>
       </c>
       <c r="F43">
-        <f>D43</f>
+        <f t="shared" si="3"/>
         <v>171.665907882683</v>
       </c>
     </row>
@@ -1395,11 +1404,11 @@
         <v>166.25779364132401</v>
       </c>
       <c r="E44">
-        <f>C44/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.069560993914251</v>
       </c>
       <c r="F44">
-        <f>D44</f>
+        <f t="shared" si="3"/>
         <v>166.25779364132401</v>
       </c>
     </row>
@@ -1417,11 +1426,11 @@
         <v>162.256715761697</v>
       </c>
       <c r="E45">
-        <f>C45/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.070550484757078</v>
       </c>
       <c r="F45">
-        <f>D45</f>
+        <f t="shared" si="3"/>
         <v>162.256715761697</v>
       </c>
     </row>
@@ -1439,11 +1448,11 @@
         <v>155.92817212181899</v>
       </c>
       <c r="E46">
-        <f>C46/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.071836822852774</v>
       </c>
       <c r="F46">
-        <f>D46</f>
+        <f t="shared" si="3"/>
         <v>155.92817212181899</v>
       </c>
     </row>
@@ -1461,11 +1470,11 @@
         <v>151.83990501959499</v>
       </c>
       <c r="E47">
-        <f>C47/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.07292526277989</v>
       </c>
       <c r="F47">
-        <f>D47</f>
+        <f t="shared" si="3"/>
         <v>151.83990501959499</v>
       </c>
     </row>
@@ -1483,11 +1492,11 @@
         <v>142.86080038470399</v>
       </c>
       <c r="E48">
-        <f>C48/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.075003193549847</v>
       </c>
       <c r="F48">
-        <f>D48</f>
+        <f t="shared" si="3"/>
         <v>142.86080038470399</v>
       </c>
     </row>
@@ -1505,11 +1514,11 @@
         <v>139.06482289528199</v>
       </c>
       <c r="E49">
-        <f>C49/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.076042158934825</v>
       </c>
       <c r="F49">
-        <f>D49</f>
+        <f t="shared" si="3"/>
         <v>139.06482289528199</v>
       </c>
     </row>
@@ -1527,11 +1536,11 @@
         <v>1641.8526339714999</v>
       </c>
       <c r="E50">
-        <f>C50/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="F50">
-        <f>D50</f>
+        <f t="shared" si="3"/>
         <v>1641.8526339714999</v>
       </c>
     </row>
@@ -1549,11 +1558,11 @@
         <v>1328.5551011037901</v>
       </c>
       <c r="E51">
-        <f>C51/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.001309978291786</v>
       </c>
       <c r="F51">
-        <f>D51</f>
+        <f t="shared" si="3"/>
         <v>1328.5551011037901</v>
       </c>
     </row>
@@ -1571,11 +1580,11 @@
         <v>1113.8060789465401</v>
       </c>
       <c r="E52">
-        <f>C52/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.002619956583573</v>
       </c>
       <c r="F52">
-        <f>D52</f>
+        <f t="shared" si="3"/>
         <v>1113.8060789465401</v>
       </c>
     </row>
@@ -1593,11 +1602,11 @@
         <v>1017.36992110687</v>
       </c>
       <c r="E53">
-        <f>C53/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.00349269033812</v>
       </c>
       <c r="F53">
-        <f>D53</f>
+        <f t="shared" si="3"/>
         <v>1017.36992110687</v>
       </c>
     </row>
@@ -1615,11 +1624,11 @@
         <v>914.99515606260695</v>
       </c>
       <c r="E54">
-        <f>C54/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.004630604807375</v>
       </c>
       <c r="F54">
-        <f>D54</f>
+        <f t="shared" si="3"/>
         <v>914.99515606260695</v>
       </c>
     </row>
@@ -1637,11 +1646,11 @@
         <v>824.67753802716595</v>
       </c>
       <c r="E55">
-        <f>C55/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.005848777978343</v>
       </c>
       <c r="F55">
-        <f>D55</f>
+        <f t="shared" si="3"/>
         <v>824.67753802716595</v>
       </c>
     </row>
@@ -1659,11 +1668,11 @@
         <v>761.993916361885</v>
       </c>
       <c r="E56">
-        <f>C56/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.006855545645408</v>
       </c>
       <c r="F56">
-        <f>D56</f>
+        <f t="shared" si="3"/>
         <v>761.993916361885</v>
       </c>
     </row>
@@ -1681,11 +1690,11 @@
         <v>699.55790721941105</v>
       </c>
       <c r="E57">
-        <f>C57/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.008150718480763</v>
       </c>
       <c r="F57">
-        <f>D57</f>
+        <f t="shared" si="3"/>
         <v>699.55790721941105</v>
       </c>
     </row>
@@ -1703,11 +1712,11 @@
         <v>657.29011629619004</v>
       </c>
       <c r="E58">
-        <f>C58/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.009169069473188</v>
       </c>
       <c r="F58">
-        <f>D58</f>
+        <f t="shared" si="3"/>
         <v>657.29011629619004</v>
       </c>
     </row>
@@ -1725,11 +1734,11 @@
         <v>619.40022908004096</v>
       </c>
       <c r="E59">
-        <f>C59/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.010290492428396</v>
       </c>
       <c r="F59">
-        <f>D59</f>
+        <f t="shared" si="3"/>
         <v>619.40022908004096</v>
       </c>
     </row>
@@ -1747,11 +1756,11 @@
         <v>589.99836072449796</v>
       </c>
       <c r="E60">
-        <f>C60/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.011359142538666</v>
       </c>
       <c r="F60">
-        <f>D60</f>
+        <f t="shared" si="3"/>
         <v>589.99836072449796</v>
       </c>
     </row>
@@ -1769,11 +1778,11 @@
         <v>563.90929531969698</v>
       </c>
       <c r="E61">
-        <f>C61/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.012427792648921</v>
       </c>
       <c r="F61">
-        <f>D61</f>
+        <f t="shared" si="3"/>
         <v>563.90929531969698</v>
       </c>
     </row>
@@ -1791,11 +1800,11 @@
         <v>539.48879562376499</v>
       </c>
       <c r="E62">
-        <f>C62/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.013526127484468</v>
       </c>
       <c r="F62">
-        <f>D62</f>
+        <f t="shared" si="3"/>
         <v>539.48879562376499</v>
       </c>
     </row>
@@ -1813,11 +1822,11 @@
         <v>516.65770358770305</v>
       </c>
       <c r="E63">
-        <f>C63/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.014559438636056</v>
       </c>
       <c r="F63">
-        <f>D63</f>
+        <f t="shared" si="3"/>
         <v>516.65770358770305</v>
       </c>
     </row>
@@ -1835,11 +1844,11 @@
         <v>495.46132638467498</v>
       </c>
       <c r="E64">
-        <f>C64/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.016043674900317</v>
       </c>
       <c r="F64">
-        <f>D64</f>
+        <f t="shared" si="3"/>
         <v>495.46132638467498</v>
       </c>
     </row>
@@ -1857,11 +1866,11 @@
         <v>474.47501632141001</v>
       </c>
       <c r="E65">
-        <f>C65/24/365+70</f>
+        <f t="shared" si="2"/>
         <v>70.017205933985551</v>
       </c>
       <c r="F65">
-        <f>D65</f>
+        <f t="shared" si="3"/>
         <v>474.47501632141001</v>
       </c>
     </row>
@@ -1879,11 +1888,11 @@
         <v>454.38725930562902</v>
       </c>
       <c r="E66">
-        <f>C66/24/365+70</f>
+        <f t="shared" ref="E66:E94" si="4">C66/24/365+70</f>
         <v>70.018342474161969</v>
       </c>
       <c r="F66">
-        <f>D66</f>
+        <f t="shared" ref="F66:F94" si="5">D66</f>
         <v>454.38725930562902</v>
       </c>
     </row>
@@ -1901,11 +1910,11 @@
         <v>440.64027127605601</v>
       </c>
       <c r="E67">
-        <f>C67/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.019393808182485</v>
       </c>
       <c r="F67">
-        <f>D67</f>
+        <f t="shared" si="5"/>
         <v>440.64027127605601</v>
       </c>
     </row>
@@ -1923,11 +1932,11 @@
         <v>424.27182832149299</v>
       </c>
       <c r="E68">
-        <f>C68/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.020680146278167</v>
       </c>
       <c r="F68">
-        <f>D68</f>
+        <f t="shared" si="5"/>
         <v>424.27182832149299</v>
       </c>
     </row>
@@ -1945,11 +1954,11 @@
         <v>413.49977955974202</v>
       </c>
       <c r="E69">
-        <f>C69/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.021768586205297</v>
       </c>
       <c r="F69">
-        <f>D69</f>
+        <f t="shared" si="5"/>
         <v>413.49977955974202</v>
       </c>
     </row>
@@ -1967,11 +1976,11 @@
         <v>401.97321499271499</v>
       </c>
       <c r="E70">
-        <f>C70/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.022857026132414</v>
       </c>
       <c r="F70">
-        <f>D70</f>
+        <f t="shared" si="5"/>
         <v>401.97321499271499</v>
       </c>
     </row>
@@ -1989,11 +1998,11 @@
         <v>379.84483973103102</v>
       </c>
       <c r="E71">
-        <f>C71/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.02394546605953</v>
       </c>
       <c r="F71">
-        <f>D71</f>
+        <f t="shared" si="5"/>
         <v>379.84483973103102</v>
       </c>
     </row>
@@ -2011,11 +2020,11 @@
         <v>368.4085793717</v>
       </c>
       <c r="E72">
-        <f>C72/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.025033905986646</v>
       </c>
       <c r="F72">
-        <f>D72</f>
+        <f t="shared" si="5"/>
         <v>368.4085793717</v>
       </c>
     </row>
@@ -2033,11 +2042,11 @@
         <v>364.28944986336501</v>
       </c>
       <c r="E73">
-        <f>C73/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.026122345913763</v>
       </c>
       <c r="F73">
-        <f>D73</f>
+        <f t="shared" si="5"/>
         <v>364.28944986336501</v>
       </c>
     </row>
@@ -2055,11 +2064,11 @@
         <v>353.970347428293</v>
       </c>
       <c r="E74">
-        <f>C74/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.027148942663203</v>
       </c>
       <c r="F74">
-        <f>D74</f>
+        <f t="shared" si="5"/>
         <v>353.970347428293</v>
       </c>
     </row>
@@ -2077,11 +2086,11 @@
         <v>168.20029523536499</v>
       </c>
       <c r="E75">
-        <f>C75/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.053570821894027</v>
       </c>
       <c r="F75">
-        <f>D75</f>
+        <f t="shared" si="5"/>
         <v>168.20029523536499</v>
       </c>
     </row>
@@ -2099,11 +2108,11 @@
         <v>163.95659018107199</v>
       </c>
       <c r="E76">
-        <f>C76/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.054831948499142</v>
       </c>
       <c r="F76">
-        <f>D76</f>
+        <f t="shared" si="5"/>
         <v>163.95659018107199</v>
       </c>
     </row>
@@ -2121,11 +2130,11 @@
         <v>158.36051683290501</v>
       </c>
       <c r="E77">
-        <f>C77/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.055954787034963</v>
       </c>
       <c r="F77">
-        <f>D77</f>
+        <f t="shared" si="5"/>
         <v>158.36051683290501</v>
       </c>
     </row>
@@ -2143,11 +2152,11 @@
         <v>158.071634346211</v>
       </c>
       <c r="E78">
-        <f>C78/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.056796562041669</v>
       </c>
       <c r="F78">
-        <f>D78</f>
+        <f t="shared" si="5"/>
         <v>158.071634346211</v>
       </c>
     </row>
@@ -2165,11 +2174,11 @@
         <v>152.00164722129099</v>
       </c>
       <c r="E79">
-        <f>C79/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.057904791785646</v>
       </c>
       <c r="F79">
-        <f>D79</f>
+        <f t="shared" si="5"/>
         <v>152.00164722129099</v>
       </c>
     </row>
@@ -2187,11 +2196,11 @@
         <v>146.734701447172</v>
       </c>
       <c r="E80">
-        <f>C80/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.058973441895915</v>
       </c>
       <c r="F80">
-        <f>D80</f>
+        <f t="shared" si="5"/>
         <v>146.734701447172</v>
       </c>
     </row>
@@ -2209,11 +2218,11 @@
         <v>142.746793442567</v>
       </c>
       <c r="E81">
-        <f>C81/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.060303757362391</v>
       </c>
       <c r="F81">
-        <f>D81</f>
+        <f t="shared" si="5"/>
         <v>142.746793442567</v>
       </c>
     </row>
@@ -2231,11 +2240,11 @@
         <v>137.51389128481799</v>
       </c>
       <c r="E82">
-        <f>C82/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.061744016255844</v>
       </c>
       <c r="F82">
-        <f>D82</f>
+        <f t="shared" si="5"/>
         <v>137.51389128481799</v>
       </c>
     </row>
@@ -2253,11 +2262,11 @@
         <v>132.56358272973699</v>
       </c>
       <c r="E83">
-        <f>C83/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.06303035435154</v>
       </c>
       <c r="F83">
-        <f>D83</f>
+        <f t="shared" si="5"/>
         <v>132.56358272973699</v>
       </c>
     </row>
@@ -2275,11 +2284,11 @@
         <v>127.489693471203</v>
       </c>
       <c r="E84">
-        <f>C84/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.064279586540607</v>
       </c>
       <c r="F84">
-        <f>D84</f>
+        <f t="shared" si="5"/>
         <v>127.489693471203</v>
       </c>
     </row>
@@ -2297,11 +2306,11 @@
         <v>123.622538580941</v>
       </c>
       <c r="E85">
-        <f>C85/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.065405132374337</v>
       </c>
       <c r="F85">
-        <f>D85</f>
+        <f t="shared" si="5"/>
         <v>123.622538580941</v>
       </c>
     </row>
@@ -2319,11 +2328,11 @@
         <v>119.316391322928</v>
       </c>
       <c r="E86">
-        <f>C86/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.066504566644156</v>
       </c>
       <c r="F86">
-        <f>D86</f>
+        <f t="shared" si="5"/>
         <v>119.316391322928</v>
       </c>
     </row>
@@ -2341,11 +2350,11 @@
         <v>116.429308588986</v>
       </c>
       <c r="E87">
-        <f>C87/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.067582012228584</v>
       </c>
       <c r="F87">
-        <f>D87</f>
+        <f t="shared" si="5"/>
         <v>116.429308588986</v>
       </c>
     </row>
@@ -2363,11 +2372,11 @@
         <v>113.28017276474201</v>
       </c>
       <c r="E88">
-        <f>C88/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.0686704521557</v>
       </c>
       <c r="F88">
-        <f>D88</f>
+        <f t="shared" si="5"/>
         <v>113.28017276474201</v>
       </c>
     </row>
@@ -2385,11 +2394,11 @@
         <v>110.122417210611</v>
       </c>
       <c r="E89">
-        <f>C89/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.069758892082817</v>
       </c>
       <c r="F89">
-        <f>D89</f>
+        <f t="shared" si="5"/>
         <v>110.122417210611</v>
       </c>
     </row>
@@ -2407,11 +2416,11 @@
         <v>106.94205691312401</v>
       </c>
       <c r="E90">
-        <f>C90/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.070827542193072</v>
       </c>
       <c r="F90">
-        <f>D90</f>
+        <f t="shared" si="5"/>
         <v>106.94205691312401</v>
       </c>
     </row>
@@ -2429,11 +2438,11 @@
         <v>103.36211598721199</v>
       </c>
       <c r="E91">
-        <f>C91/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.071935771937049</v>
       </c>
       <c r="F91">
-        <f>D91</f>
+        <f t="shared" si="5"/>
         <v>103.36211598721199</v>
       </c>
     </row>
@@ -2451,11 +2460,11 @@
         <v>100.737803743958</v>
       </c>
       <c r="E92">
-        <f>C92/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.07302421186418</v>
       </c>
       <c r="F92">
-        <f>D92</f>
+        <f t="shared" si="5"/>
         <v>100.737803743958</v>
       </c>
     </row>
@@ -2473,11 +2482,11 @@
         <v>97.3523393590594</v>
       </c>
       <c r="E93">
-        <f>C93/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.07403569139241</v>
       </c>
       <c r="F93">
-        <f>D93</f>
+        <f t="shared" si="5"/>
         <v>97.3523393590594</v>
       </c>
     </row>
@@ -2495,17 +2504,4109 @@
         <v>95.115885995525602</v>
       </c>
       <c r="E94">
-        <f>C94/24/365+70</f>
+        <f t="shared" si="4"/>
         <v>70.075151617176274</v>
       </c>
       <c r="F94">
-        <f>D94</f>
+        <f t="shared" si="5"/>
         <v>95.115885995525602</v>
       </c>
     </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95">
+        <v>1.6393442622950201</v>
+      </c>
+      <c r="D95">
+        <v>492.38826317067299</v>
+      </c>
+      <c r="E95">
+        <f>C95/24/365+70</f>
+        <v>70.000187139755965</v>
+      </c>
+      <c r="F95">
+        <f>D95</f>
+        <v>492.38826317067299</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96">
+        <v>11.4754098360656</v>
+      </c>
+      <c r="D96">
+        <v>398.384697447983</v>
+      </c>
+      <c r="E96">
+        <f>C96/24/365+70</f>
+        <v>70.001309978291786</v>
+      </c>
+      <c r="F96">
+        <f>D96</f>
+        <v>398.384697447983</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97">
+        <v>18.032786885245901</v>
+      </c>
+      <c r="D97">
+        <v>358.38561333350799</v>
+      </c>
+      <c r="E97">
+        <f>C97/24/365+70</f>
+        <v>70.002058537315662</v>
+      </c>
+      <c r="F97">
+        <f>D97</f>
+        <v>358.38561333350799</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98">
+        <v>29.508196721311599</v>
+      </c>
+      <c r="D98">
+        <v>311.29001863397599</v>
+      </c>
+      <c r="E98">
+        <f>C98/24/365+70</f>
+        <v>70.003368515607463</v>
+      </c>
+      <c r="F98">
+        <f>D98</f>
+        <v>311.29001863397599</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99">
+        <v>36.403487016690796</v>
+      </c>
+      <c r="D99">
+        <v>284.34403561174599</v>
+      </c>
+      <c r="E99">
+        <f>C99/24/365+70</f>
+        <v>70.004155649202815</v>
+      </c>
+      <c r="F99">
+        <f>D99</f>
+        <v>284.34403561174599</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100">
+        <v>45.938220778254298</v>
+      </c>
+      <c r="D100">
+        <v>256.68328860005801</v>
+      </c>
+      <c r="E100">
+        <f>C100/24/365+70</f>
+        <v>70.005244089129931</v>
+      </c>
+      <c r="F100">
+        <f>D100</f>
+        <v>256.68328860005801</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101">
+        <v>55.472954539817898</v>
+      </c>
+      <c r="D101">
+        <v>235.291690293861</v>
+      </c>
+      <c r="E101">
+        <f>C101/24/365+70</f>
+        <v>70.006332529057062</v>
+      </c>
+      <c r="F101">
+        <f>D101</f>
+        <v>235.291690293861</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102">
+        <v>65.007688301381194</v>
+      </c>
+      <c r="D102">
+        <v>217.89767676816101</v>
+      </c>
+      <c r="E102">
+        <f>C102/24/365+70</f>
+        <v>70.007420968984178</v>
+      </c>
+      <c r="F102">
+        <f>D102</f>
+        <v>217.89767676816101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103">
+        <v>74.542422062944695</v>
+      </c>
+      <c r="D103">
+        <v>203.11096511015</v>
+      </c>
+      <c r="E103">
+        <f>C103/24/365+70</f>
+        <v>70.008509408911294</v>
+      </c>
+      <c r="F103">
+        <f>D103</f>
+        <v>203.11096511015</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" t="s">
+        <v>9</v>
+      </c>
+      <c r="C104">
+        <v>84.077155824508196</v>
+      </c>
+      <c r="D104">
+        <v>191.54349486320001</v>
+      </c>
+      <c r="E104">
+        <f>C104/24/365+70</f>
+        <v>70.009597848838411</v>
+      </c>
+      <c r="F104">
+        <f>D104</f>
+        <v>191.54349486320001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105">
+        <v>93.611889586071499</v>
+      </c>
+      <c r="D105">
+        <v>180.89130702656601</v>
+      </c>
+      <c r="E105">
+        <f>C105/24/365+70</f>
+        <v>70.010686288765527</v>
+      </c>
+      <c r="F105">
+        <f>D105</f>
+        <v>180.89130702656601</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106">
+        <v>103.146623347635</v>
+      </c>
+      <c r="D106">
+        <v>172.43890260953799</v>
+      </c>
+      <c r="E106">
+        <f>C106/24/365+70</f>
+        <v>70.011774728692657</v>
+      </c>
+      <c r="F106">
+        <f>D106</f>
+        <v>172.43890260953799</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107">
+        <v>112.681357109198</v>
+      </c>
+      <c r="D107">
+        <v>164.94220994953599</v>
+      </c>
+      <c r="E107">
+        <f>C107/24/365+70</f>
+        <v>70.012863168619774</v>
+      </c>
+      <c r="F107">
+        <f>D107</f>
+        <v>164.94220994953599</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108">
+        <v>122.21609087076099</v>
+      </c>
+      <c r="D108">
+        <v>157.905813384845</v>
+      </c>
+      <c r="E108">
+        <f>C108/24/365+70</f>
+        <v>70.01395160854689</v>
+      </c>
+      <c r="F108">
+        <f>D108</f>
+        <v>157.905813384845</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" t="s">
+        <v>9</v>
+      </c>
+      <c r="C109">
+        <v>131.75082463232499</v>
+      </c>
+      <c r="D109">
+        <v>151.42721381823901</v>
+      </c>
+      <c r="E109">
+        <f>C109/24/365+70</f>
+        <v>70.015040048474006</v>
+      </c>
+      <c r="F109">
+        <f>D109</f>
+        <v>151.42721381823901</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>3</v>
+      </c>
+      <c r="B110" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110">
+        <v>141.285558393889</v>
+      </c>
+      <c r="D110">
+        <v>146.45602981924301</v>
+      </c>
+      <c r="E110">
+        <f>C110/24/365+70</f>
+        <v>70.016128488401122</v>
+      </c>
+      <c r="F110">
+        <f>D110</f>
+        <v>146.45602981924301</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>3</v>
+      </c>
+      <c r="B111" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111">
+        <v>150.82029215545199</v>
+      </c>
+      <c r="D111">
+        <v>140.68654751299201</v>
+      </c>
+      <c r="E111">
+        <f>C111/24/365+70</f>
+        <v>70.017216928328253</v>
+      </c>
+      <c r="F111">
+        <f>D111</f>
+        <v>140.68654751299201</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112">
+        <v>160.35502591701501</v>
+      </c>
+      <c r="D112">
+        <v>136.06796742929501</v>
+      </c>
+      <c r="E112">
+        <f>C112/24/365+70</f>
+        <v>70.018305368255369</v>
+      </c>
+      <c r="F112">
+        <f>D112</f>
+        <v>136.06796742929501</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113">
+        <v>169.889759678579</v>
+      </c>
+      <c r="D113">
+        <v>132.27498786894901</v>
+      </c>
+      <c r="E113">
+        <f>C113/24/365+70</f>
+        <v>70.019393808182485</v>
+      </c>
+      <c r="F113">
+        <f>D113</f>
+        <v>132.27498786894901</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>3</v>
+      </c>
+      <c r="B114" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114">
+        <v>179.42449344014199</v>
+      </c>
+      <c r="D114">
+        <v>127.497611992911</v>
+      </c>
+      <c r="E114">
+        <f>C114/24/365+70</f>
+        <v>70.020482248109602</v>
+      </c>
+      <c r="F114">
+        <f>D114</f>
+        <v>127.497611992911</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" t="s">
+        <v>9</v>
+      </c>
+      <c r="C115">
+        <v>188.959227201706</v>
+      </c>
+      <c r="D115">
+        <v>123.94353644215001</v>
+      </c>
+      <c r="E115">
+        <f>C115/24/365+70</f>
+        <v>70.021570688036718</v>
+      </c>
+      <c r="F115">
+        <f>D115</f>
+        <v>123.94353644215001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116">
+        <v>198.49396096326899</v>
+      </c>
+      <c r="D116">
+        <v>119.77259459171501</v>
+      </c>
+      <c r="E116">
+        <f>C116/24/365+70</f>
+        <v>70.022659127963848</v>
+      </c>
+      <c r="F116">
+        <f>D116</f>
+        <v>119.77259459171501</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" t="s">
+        <v>9</v>
+      </c>
+      <c r="C117">
+        <v>208.028694724833</v>
+      </c>
+      <c r="D117">
+        <v>116.63228741338899</v>
+      </c>
+      <c r="E117">
+        <f>C117/24/365+70</f>
+        <v>70.023747567890965</v>
+      </c>
+      <c r="F117">
+        <f>D117</f>
+        <v>116.63228741338899</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118">
+        <v>217.56342848639599</v>
+      </c>
+      <c r="D118">
+        <v>112.133107965958</v>
+      </c>
+      <c r="E118">
+        <f>C118/24/365+70</f>
+        <v>70.024836007818081</v>
+      </c>
+      <c r="F118">
+        <f>D118</f>
+        <v>112.133107965958</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" t="s">
+        <v>9</v>
+      </c>
+      <c r="C119">
+        <v>227.09816224796</v>
+      </c>
+      <c r="D119">
+        <v>109.565594667334</v>
+      </c>
+      <c r="E119">
+        <f>C119/24/365+70</f>
+        <v>70.025924447745197</v>
+      </c>
+      <c r="F119">
+        <f>D119</f>
+        <v>109.565594667334</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>3</v>
+      </c>
+      <c r="B120" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120">
+        <v>236.63289600952299</v>
+      </c>
+      <c r="D120">
+        <v>105.608413969453</v>
+      </c>
+      <c r="E120">
+        <f>C120/24/365+70</f>
+        <v>70.027012887672313</v>
+      </c>
+      <c r="F120">
+        <f>D120</f>
+        <v>105.608413969453</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>3</v>
+      </c>
+      <c r="B121" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121">
+        <v>244.00064482527699</v>
+      </c>
+      <c r="D121">
+        <v>103.51172939668101</v>
+      </c>
+      <c r="E121">
+        <f>C121/24/365+70</f>
+        <v>70.027853954888727</v>
+      </c>
+      <c r="F121">
+        <f>D121</f>
+        <v>103.51172939668101</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122">
+        <v>460.26574241710199</v>
+      </c>
+      <c r="D122">
+        <v>51.901712947636497</v>
+      </c>
+      <c r="E122">
+        <f>C122/24/365+70</f>
+        <v>70.052541751417479</v>
+      </c>
+      <c r="F122">
+        <f>D122</f>
+        <v>51.901712947636497</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>3</v>
+      </c>
+      <c r="B123" t="s">
+        <v>9</v>
+      </c>
+      <c r="C123">
+        <v>469.80047617866597</v>
+      </c>
+      <c r="D123">
+        <v>50.713318720171699</v>
+      </c>
+      <c r="E123">
+        <f>C123/24/365+70</f>
+        <v>70.053630191344595</v>
+      </c>
+      <c r="F123">
+        <f>D123</f>
+        <v>50.713318720171699</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>3</v>
+      </c>
+      <c r="B124" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124">
+        <v>479.33520994022899</v>
+      </c>
+      <c r="D124">
+        <v>49.509965241315399</v>
+      </c>
+      <c r="E124">
+        <f>C124/24/365+70</f>
+        <v>70.054718631271712</v>
+      </c>
+      <c r="F124">
+        <f>D124</f>
+        <v>49.509965241315399</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>3</v>
+      </c>
+      <c r="B125" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125">
+        <v>480.26868037842399</v>
+      </c>
+      <c r="D125">
+        <v>11.018959508087701</v>
+      </c>
+      <c r="E125">
+        <f>C125/24/365+70</f>
+        <v>70.054825191824023</v>
+      </c>
+      <c r="F125">
+        <f>D125</f>
+        <v>11.018959508087701</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>3</v>
+      </c>
+      <c r="B126" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126">
+        <v>488.86994370179201</v>
+      </c>
+      <c r="D126">
+        <v>47.8438583028952</v>
+      </c>
+      <c r="E126">
+        <f>C126/24/365+70</f>
+        <v>70.055807071198828</v>
+      </c>
+      <c r="F126">
+        <f>D126</f>
+        <v>47.8438583028952</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>3</v>
+      </c>
+      <c r="B127" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127">
+        <v>498.40467746335599</v>
+      </c>
+      <c r="D127">
+        <v>46.748376828436797</v>
+      </c>
+      <c r="E127">
+        <f>C127/24/365+70</f>
+        <v>70.056895511125958</v>
+      </c>
+      <c r="F127">
+        <f>D127</f>
+        <v>46.748376828436797</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>3</v>
+      </c>
+      <c r="B128" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128">
+        <v>507.93941122491901</v>
+      </c>
+      <c r="D128">
+        <v>44.983304292364799</v>
+      </c>
+      <c r="E128">
+        <f>C128/24/365+70</f>
+        <v>70.057983951053075</v>
+      </c>
+      <c r="F128">
+        <f>D128</f>
+        <v>44.983304292364799</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A129" t="s">
+        <v>3</v>
+      </c>
+      <c r="B129" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129">
+        <v>517.474144986483</v>
+      </c>
+      <c r="D129">
+        <v>44.028227006749198</v>
+      </c>
+      <c r="E129">
+        <f>C129/24/365+70</f>
+        <v>70.059072390980191</v>
+      </c>
+      <c r="F129">
+        <f>D129</f>
+        <v>44.028227006749198</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>3</v>
+      </c>
+      <c r="B130" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130">
+        <v>527.00887874804596</v>
+      </c>
+      <c r="D130">
+        <v>42.4742059461773</v>
+      </c>
+      <c r="E130">
+        <f>C130/24/365+70</f>
+        <v>70.060160830907307</v>
+      </c>
+      <c r="F130">
+        <f>D130</f>
+        <v>42.4742059461773</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
+        <v>3</v>
+      </c>
+      <c r="B131" t="s">
+        <v>9</v>
+      </c>
+      <c r="C131">
+        <v>536.54361250961006</v>
+      </c>
+      <c r="D131">
+        <v>41.360578456674098</v>
+      </c>
+      <c r="E131">
+        <f>C131/24/365+70</f>
+        <v>70.061249270834423</v>
+      </c>
+      <c r="F131">
+        <f>D131</f>
+        <v>41.360578456674098</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A132" t="s">
+        <v>3</v>
+      </c>
+      <c r="B132" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132">
+        <v>546.07834627117302</v>
+      </c>
+      <c r="D132">
+        <v>40.139220518624803</v>
+      </c>
+      <c r="E132">
+        <f>C132/24/365+70</f>
+        <v>70.062337710761554</v>
+      </c>
+      <c r="F132">
+        <f>D132</f>
+        <v>40.139220518624803</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>3</v>
+      </c>
+      <c r="B133" t="s">
+        <v>9</v>
+      </c>
+      <c r="C133">
+        <v>555.613080032737</v>
+      </c>
+      <c r="D133">
+        <v>39.053550090582803</v>
+      </c>
+      <c r="E133">
+        <f>C133/24/365+70</f>
+        <v>70.06342615068867</v>
+      </c>
+      <c r="F133">
+        <f>D133</f>
+        <v>39.053550090582803</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A134" t="s">
+        <v>3</v>
+      </c>
+      <c r="B134" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134">
+        <v>565.14781379429996</v>
+      </c>
+      <c r="D134">
+        <v>37.835837069725699</v>
+      </c>
+      <c r="E134">
+        <f>C134/24/365+70</f>
+        <v>70.064514590615786</v>
+      </c>
+      <c r="F134">
+        <f>D134</f>
+        <v>37.835837069725699</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A135" t="s">
+        <v>3</v>
+      </c>
+      <c r="B135" t="s">
+        <v>9</v>
+      </c>
+      <c r="C135">
+        <v>574.68254755586395</v>
+      </c>
+      <c r="D135">
+        <v>36.718563045227697</v>
+      </c>
+      <c r="E135">
+        <f>C135/24/365+70</f>
+        <v>70.065603030542903</v>
+      </c>
+      <c r="F135">
+        <f>D135</f>
+        <v>36.718563045227697</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A136" t="s">
+        <v>3</v>
+      </c>
+      <c r="B136" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136">
+        <v>584.21728131742702</v>
+      </c>
+      <c r="D136">
+        <v>35.664632951767999</v>
+      </c>
+      <c r="E136">
+        <f>C136/24/365+70</f>
+        <v>70.066691470470019</v>
+      </c>
+      <c r="F136">
+        <f>D136</f>
+        <v>35.664632951767999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A137" t="s">
+        <v>3</v>
+      </c>
+      <c r="B137" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137">
+        <v>593.75201507899101</v>
+      </c>
+      <c r="D137">
+        <v>34.611473537934202</v>
+      </c>
+      <c r="E137">
+        <f>C137/24/365+70</f>
+        <v>70.067779910397149</v>
+      </c>
+      <c r="F137">
+        <f>D137</f>
+        <v>34.611473537934202</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A138" t="s">
+        <v>3</v>
+      </c>
+      <c r="B138" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138">
+        <v>603.28674884055397</v>
+      </c>
+      <c r="D138">
+        <v>33.618023072683599</v>
+      </c>
+      <c r="E138">
+        <f>C138/24/365+70</f>
+        <v>70.068868350324266</v>
+      </c>
+      <c r="F138">
+        <f>D138</f>
+        <v>33.618023072683599</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A139" t="s">
+        <v>3</v>
+      </c>
+      <c r="B139" t="s">
+        <v>9</v>
+      </c>
+      <c r="C139">
+        <v>612.82148260211704</v>
+      </c>
+      <c r="D139">
+        <v>32.569793031211603</v>
+      </c>
+      <c r="E139">
+        <f>C139/24/365+70</f>
+        <v>70.069956790251382</v>
+      </c>
+      <c r="F139">
+        <f>D139</f>
+        <v>32.569793031211603</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A140" t="s">
+        <v>3</v>
+      </c>
+      <c r="B140" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140">
+        <v>622.35621636368103</v>
+      </c>
+      <c r="D140">
+        <v>31.6618897121127</v>
+      </c>
+      <c r="E140">
+        <f>C140/24/365+70</f>
+        <v>70.071045230178498</v>
+      </c>
+      <c r="F140">
+        <f>D140</f>
+        <v>31.6618897121127</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A141" t="s">
+        <v>3</v>
+      </c>
+      <c r="B141" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141">
+        <v>631.89095012524399</v>
+      </c>
+      <c r="D141">
+        <v>30.622465717270099</v>
+      </c>
+      <c r="E141">
+        <f>C141/24/365+70</f>
+        <v>70.072133670105615</v>
+      </c>
+      <c r="F141">
+        <f>D141</f>
+        <v>30.622465717270099</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A142" t="s">
+        <v>3</v>
+      </c>
+      <c r="B142" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142">
+        <v>641.42568388680797</v>
+      </c>
+      <c r="D142">
+        <v>29.895839032564901</v>
+      </c>
+      <c r="E142">
+        <f>C142/24/365+70</f>
+        <v>70.073222110032745</v>
+      </c>
+      <c r="F142">
+        <f>D142</f>
+        <v>29.895839032564901</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>3</v>
+      </c>
+      <c r="B143" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143">
+        <v>650.96041764837105</v>
+      </c>
+      <c r="D143">
+        <v>28.767065629097601</v>
+      </c>
+      <c r="E143">
+        <f>C143/24/365+70</f>
+        <v>70.074310549959861</v>
+      </c>
+      <c r="F143">
+        <f>D143</f>
+        <v>28.767065629097601</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A144" t="s">
+        <v>3</v>
+      </c>
+      <c r="B144" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144">
+        <v>660.49515140993503</v>
+      </c>
+      <c r="D144">
+        <v>28.156288555506102</v>
+      </c>
+      <c r="E144">
+        <f>C144/24/365+70</f>
+        <v>70.075398989886978</v>
+      </c>
+      <c r="F144">
+        <f>D144</f>
+        <v>28.156288555506102</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A145" t="s">
+        <v>3</v>
+      </c>
+      <c r="B145" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145">
+        <v>667.42950323652599</v>
+      </c>
+      <c r="D145">
+        <v>27.338427287750701</v>
+      </c>
+      <c r="E145">
+        <f>C145/24/365+70</f>
+        <v>70.076190582561253</v>
+      </c>
+      <c r="F145">
+        <f>D145</f>
+        <v>27.338427287750701</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A146" t="s">
+        <v>3</v>
+      </c>
+      <c r="B146" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146">
+        <v>1.7317278837329</v>
+      </c>
+      <c r="D146">
+        <v>153.798800894463</v>
+      </c>
+      <c r="E146">
+        <f>C146/24/365+70</f>
+        <v>70.00019768583148</v>
+      </c>
+      <c r="F146">
+        <f>D146</f>
+        <v>153.798800894463</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A147" t="s">
+        <v>3</v>
+      </c>
+      <c r="B147" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147">
+        <v>9.1613905550811907</v>
+      </c>
+      <c r="D147">
+        <v>132.10793606257599</v>
+      </c>
+      <c r="E147">
+        <f>C147/24/365+70</f>
+        <v>70.001045820839622</v>
+      </c>
+      <c r="F147">
+        <f>D147</f>
+        <v>132.10793606257599</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A148" t="s">
+        <v>3</v>
+      </c>
+      <c r="B148" t="s">
+        <v>10</v>
+      </c>
+      <c r="C148">
+        <v>19.067607450211799</v>
+      </c>
+      <c r="D148">
+        <v>114.82679748802001</v>
+      </c>
+      <c r="E148">
+        <f>C148/24/365+70</f>
+        <v>70.002176667517148</v>
+      </c>
+      <c r="F148">
+        <f>D148</f>
+        <v>114.82679748802001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
+        <v>3</v>
+      </c>
+      <c r="B149" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149">
+        <v>28.6023412117754</v>
+      </c>
+      <c r="D149">
+        <v>102.43915449059701</v>
+      </c>
+      <c r="E149">
+        <f>C149/24/365+70</f>
+        <v>70.003265107444264</v>
+      </c>
+      <c r="F149">
+        <f>D149</f>
+        <v>102.43915449059701</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A150" t="s">
+        <v>3</v>
+      </c>
+      <c r="B150" t="s">
+        <v>10</v>
+      </c>
+      <c r="C150">
+        <v>38.137074973338898</v>
+      </c>
+      <c r="D150">
+        <v>92.196943584369507</v>
+      </c>
+      <c r="E150">
+        <f>C150/24/365+70</f>
+        <v>70.00435354737138</v>
+      </c>
+      <c r="F150">
+        <f>D150</f>
+        <v>92.196943584369507</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A151" t="s">
+        <v>3</v>
+      </c>
+      <c r="B151" t="s">
+        <v>10</v>
+      </c>
+      <c r="C151">
+        <v>57.206542496465701</v>
+      </c>
+      <c r="D151">
+        <v>76.944308942737194</v>
+      </c>
+      <c r="E151">
+        <f>C151/24/365+70</f>
+        <v>70.006530427225627</v>
+      </c>
+      <c r="F151">
+        <f>D151</f>
+        <v>76.944308942737194</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A152" t="s">
+        <v>3</v>
+      </c>
+      <c r="B152" t="s">
+        <v>10</v>
+      </c>
+      <c r="C152">
+        <v>66.741276258029302</v>
+      </c>
+      <c r="D152">
+        <v>71.134946809749394</v>
+      </c>
+      <c r="E152">
+        <f>C152/24/365+70</f>
+        <v>70.007618867152743</v>
+      </c>
+      <c r="F152">
+        <f>D152</f>
+        <v>71.134946809749394</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A153" t="s">
+        <v>3</v>
+      </c>
+      <c r="B153" t="s">
+        <v>10</v>
+      </c>
+      <c r="C153">
+        <v>78.529674363234705</v>
+      </c>
+      <c r="D153">
+        <v>65.590158899489097</v>
+      </c>
+      <c r="E153">
+        <f>C153/24/365+70</f>
+        <v>70.008964574698993</v>
+      </c>
+      <c r="F153">
+        <f>D153</f>
+        <v>65.590158899489097</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A154" t="s">
+        <v>3</v>
+      </c>
+      <c r="B154" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154">
+        <v>87.544331737803901</v>
+      </c>
+      <c r="D154">
+        <v>62.0910230416142</v>
+      </c>
+      <c r="E154">
+        <f>C154/24/365+70</f>
+        <v>70.009993645175555</v>
+      </c>
+      <c r="F154">
+        <f>D154</f>
+        <v>62.0910230416142</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A155" t="s">
+        <v>3</v>
+      </c>
+      <c r="B155" t="s">
+        <v>10</v>
+      </c>
+      <c r="C155">
+        <v>97.9458594776913</v>
+      </c>
+      <c r="D155">
+        <v>58.613864810574498</v>
+      </c>
+      <c r="E155">
+        <f>C155/24/365+70</f>
+        <v>70.011181034186947</v>
+      </c>
+      <c r="F155">
+        <f>D155</f>
+        <v>58.613864810574498</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
+        <v>3</v>
+      </c>
+      <c r="B156" t="s">
+        <v>10</v>
+      </c>
+      <c r="C156">
+        <v>108.154766333506</v>
+      </c>
+      <c r="D156">
+        <v>55.745725100827997</v>
+      </c>
+      <c r="E156">
+        <f>C156/24/365+70</f>
+        <v>70.012346434512963</v>
+      </c>
+      <c r="F156">
+        <f>D156</f>
+        <v>55.745725100827997</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
+        <v>3</v>
+      </c>
+      <c r="B157" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157">
+        <v>117.015327000818</v>
+      </c>
+      <c r="D157">
+        <v>53.323192393091396</v>
+      </c>
+      <c r="E157">
+        <f>C157/24/365+70</f>
+        <v>70.013357914041194</v>
+      </c>
+      <c r="F157">
+        <f>D157</f>
+        <v>53.323192393091396</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A158" t="s">
+        <v>3</v>
+      </c>
+      <c r="B158" t="s">
+        <v>10</v>
+      </c>
+      <c r="C158">
+        <v>126.55006076238099</v>
+      </c>
+      <c r="D158">
+        <v>51.384192620672401</v>
+      </c>
+      <c r="E158">
+        <f>C158/24/365+70</f>
+        <v>70.01444635396831</v>
+      </c>
+      <c r="F158">
+        <f>D158</f>
+        <v>51.384192620672401</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A159" t="s">
+        <v>3</v>
+      </c>
+      <c r="B159" t="s">
+        <v>10</v>
+      </c>
+      <c r="C159">
+        <v>138.685176458917</v>
+      </c>
+      <c r="D159">
+        <v>48.9088667242764</v>
+      </c>
+      <c r="E159">
+        <f>C159/24/365+70</f>
+        <v>70.015831641148282</v>
+      </c>
+      <c r="F159">
+        <f>D159</f>
+        <v>48.9088667242764</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A160" t="s">
+        <v>3</v>
+      </c>
+      <c r="B160" t="s">
+        <v>10</v>
+      </c>
+      <c r="C160">
+        <v>148.21991022047999</v>
+      </c>
+      <c r="D160">
+        <v>47.127376424722002</v>
+      </c>
+      <c r="E160">
+        <f>C160/24/365+70</f>
+        <v>70.016920081075398</v>
+      </c>
+      <c r="F160">
+        <f>D160</f>
+        <v>47.127376424722002</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A161" t="s">
+        <v>3</v>
+      </c>
+      <c r="B161" t="s">
+        <v>10</v>
+      </c>
+      <c r="C161">
+        <v>157.75464398204301</v>
+      </c>
+      <c r="D161">
+        <v>45.633627882528799</v>
+      </c>
+      <c r="E161">
+        <f>C161/24/365+70</f>
+        <v>70.018008521002514</v>
+      </c>
+      <c r="F161">
+        <f>D161</f>
+        <v>45.633627882528799</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A162" t="s">
+        <v>3</v>
+      </c>
+      <c r="B162" t="s">
+        <v>10</v>
+      </c>
+      <c r="C162">
+        <v>167.93947322734999</v>
+      </c>
+      <c r="D162">
+        <v>43.889306917450597</v>
+      </c>
+      <c r="E162">
+        <f>C162/24/365+70</f>
+        <v>70.019171172742844</v>
+      </c>
+      <c r="F162">
+        <f>D162</f>
+        <v>43.889306917450597</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A163" t="s">
+        <v>3</v>
+      </c>
+      <c r="B163" t="s">
+        <v>10</v>
+      </c>
+      <c r="C163">
+        <v>176.82411150517001</v>
+      </c>
+      <c r="D163">
+        <v>42.686608137582198</v>
+      </c>
+      <c r="E163">
+        <f>C163/24/365+70</f>
+        <v>70.020185400856761</v>
+      </c>
+      <c r="F163">
+        <f>D163</f>
+        <v>42.686608137582198</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A164" t="s">
+        <v>3</v>
+      </c>
+      <c r="B164" t="s">
+        <v>10</v>
+      </c>
+      <c r="C164">
+        <v>188.959227201706</v>
+      </c>
+      <c r="D164">
+        <v>40.907950363543002</v>
+      </c>
+      <c r="E164">
+        <f>C164/24/365+70</f>
+        <v>70.021570688036718</v>
+      </c>
+      <c r="F164">
+        <f>D164</f>
+        <v>40.907950363543002</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A165" t="s">
+        <v>3</v>
+      </c>
+      <c r="B165" t="s">
+        <v>10</v>
+      </c>
+      <c r="C165">
+        <v>196.76037300662099</v>
+      </c>
+      <c r="D165">
+        <v>39.946932282101301</v>
+      </c>
+      <c r="E165">
+        <f>C165/24/365+70</f>
+        <v>70.022461229795283</v>
+      </c>
+      <c r="F165">
+        <f>D165</f>
+        <v>39.946932282101301</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A166" t="s">
+        <v>3</v>
+      </c>
+      <c r="B166" t="s">
+        <v>10</v>
+      </c>
+      <c r="C166">
+        <v>208.028694724833</v>
+      </c>
+      <c r="D166">
+        <v>38.801958052698801</v>
+      </c>
+      <c r="E166">
+        <f>C166/24/365+70</f>
+        <v>70.023747567890965</v>
+      </c>
+      <c r="F166">
+        <f>D166</f>
+        <v>38.801958052698801</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A167" t="s">
+        <v>3</v>
+      </c>
+      <c r="B167" t="s">
+        <v>10</v>
+      </c>
+      <c r="C167">
+        <v>226.23136826963599</v>
+      </c>
+      <c r="D167">
+        <v>36.252721957317704</v>
+      </c>
+      <c r="E167">
+        <f>C167/24/365+70</f>
+        <v>70.025825498660922</v>
+      </c>
+      <c r="F167">
+        <f>D167</f>
+        <v>36.252721957317704</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A168" t="s">
+        <v>3</v>
+      </c>
+      <c r="B168" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168">
+        <v>234.46591106371301</v>
+      </c>
+      <c r="D168">
+        <v>35.302720050655999</v>
+      </c>
+      <c r="E168">
+        <f>C168/24/365+70</f>
+        <v>70.02676551496161</v>
+      </c>
+      <c r="F168">
+        <f>D168</f>
+        <v>35.302720050655999</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A169" t="s">
+        <v>3</v>
+      </c>
+      <c r="B169" t="s">
+        <v>10</v>
+      </c>
+      <c r="C169">
+        <v>247.03442374941</v>
+      </c>
+      <c r="D169">
+        <v>33.915686484838403</v>
+      </c>
+      <c r="E169">
+        <f>C169/24/365+70</f>
+        <v>70.028200276683719</v>
+      </c>
+      <c r="F169">
+        <f>D169</f>
+        <v>33.915686484838403</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A170" t="s">
+        <v>3</v>
+      </c>
+      <c r="B170" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170">
+        <v>255.59401428535901</v>
+      </c>
+      <c r="D170">
+        <v>33.073412526470797</v>
+      </c>
+      <c r="E170">
+        <f>C170/24/365+70</f>
+        <v>70.029177398891022</v>
+      </c>
+      <c r="F170">
+        <f>D170</f>
+        <v>33.073412526470797</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A171" t="s">
+        <v>3</v>
+      </c>
+      <c r="B171" t="s">
+        <v>10</v>
+      </c>
+      <c r="C171">
+        <v>266.103891272537</v>
+      </c>
+      <c r="D171">
+        <v>31.942232970447598</v>
+      </c>
+      <c r="E171">
+        <f>C171/24/365+70</f>
+        <v>70.030377156537966</v>
+      </c>
+      <c r="F171">
+        <f>D171</f>
+        <v>31.942232970447598</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A172" t="s">
+        <v>3</v>
+      </c>
+      <c r="B172" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172">
+        <v>274.66348180848598</v>
+      </c>
+      <c r="D172">
+        <v>31.089356173949302</v>
+      </c>
+      <c r="E172">
+        <f>C172/24/365+70</f>
+        <v>70.031354278745255</v>
+      </c>
+      <c r="F172">
+        <f>D172</f>
+        <v>31.089356173949302</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A173" t="s">
+        <v>3</v>
+      </c>
+      <c r="B173" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173">
+        <v>285.173358795664</v>
+      </c>
+      <c r="D173">
+        <v>30.083608880936701</v>
+      </c>
+      <c r="E173">
+        <f>C173/24/365+70</f>
+        <v>70.032554036392199</v>
+      </c>
+      <c r="F173">
+        <f>D173</f>
+        <v>30.083608880936701</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A174" t="s">
+        <v>3</v>
+      </c>
+      <c r="B174" t="s">
+        <v>10</v>
+      </c>
+      <c r="C174">
+        <v>292.97450460058002</v>
+      </c>
+      <c r="D174">
+        <v>29.409053085516099</v>
+      </c>
+      <c r="E174">
+        <f>C174/24/365+70</f>
+        <v>70.03344457815075</v>
+      </c>
+      <c r="F174">
+        <f>D174</f>
+        <v>29.409053085516099</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A175" t="s">
+        <v>3</v>
+      </c>
+      <c r="B175" t="s">
+        <v>10</v>
+      </c>
+      <c r="C175">
+        <v>304.242826318791</v>
+      </c>
+      <c r="D175">
+        <v>28.309020527835902</v>
+      </c>
+      <c r="E175">
+        <f>C175/24/365+70</f>
+        <v>70.034730916246431</v>
+      </c>
+      <c r="F175">
+        <f>D175</f>
+        <v>28.309020527835902</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A176" t="s">
+        <v>3</v>
+      </c>
+      <c r="B176" t="s">
+        <v>10</v>
+      </c>
+      <c r="C176">
+        <v>312.04397212370702</v>
+      </c>
+      <c r="D176">
+        <v>27.691090496826298</v>
+      </c>
+      <c r="E176">
+        <f>C176/24/365+70</f>
+        <v>70.035621458004982</v>
+      </c>
+      <c r="F176">
+        <f>D176</f>
+        <v>27.691090496826298</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A177" t="s">
+        <v>3</v>
+      </c>
+      <c r="B177" t="s">
+        <v>10</v>
+      </c>
+      <c r="C177">
+        <v>323.31229384191801</v>
+      </c>
+      <c r="D177">
+        <v>26.729987646504402</v>
+      </c>
+      <c r="E177">
+        <f>C177/24/365+70</f>
+        <v>70.036907796100678</v>
+      </c>
+      <c r="F177">
+        <f>D177</f>
+        <v>26.729987646504402</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A178" t="s">
+        <v>3</v>
+      </c>
+      <c r="B178" t="s">
+        <v>10</v>
+      </c>
+      <c r="C178">
+        <v>331.54683663599599</v>
+      </c>
+      <c r="D178">
+        <v>26.065565556286501</v>
+      </c>
+      <c r="E178">
+        <f>C178/24/365+70</f>
+        <v>70.037847812401367</v>
+      </c>
+      <c r="F178">
+        <f>D178</f>
+        <v>26.065565556286501</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A179" t="s">
+        <v>3</v>
+      </c>
+      <c r="B179" t="s">
+        <v>10</v>
+      </c>
+      <c r="C179">
+        <v>343.24855534336899</v>
+      </c>
+      <c r="D179">
+        <v>25.090602167501999</v>
+      </c>
+      <c r="E179">
+        <f>C179/24/365+70</f>
+        <v>70.0391836250392</v>
+      </c>
+      <c r="F179">
+        <f>D179</f>
+        <v>25.090602167501999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A180" t="s">
+        <v>3</v>
+      </c>
+      <c r="B180" t="s">
+        <v>10</v>
+      </c>
+      <c r="C180">
+        <v>351.04970114828399</v>
+      </c>
+      <c r="D180">
+        <v>24.486273123794099</v>
+      </c>
+      <c r="E180">
+        <f>C180/24/365+70</f>
+        <v>70.040074166797751</v>
+      </c>
+      <c r="F180">
+        <f>D180</f>
+        <v>24.486273123794099</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A181" t="s">
+        <v>3</v>
+      </c>
+      <c r="B181" t="s">
+        <v>10</v>
+      </c>
+      <c r="C181">
+        <v>362.31802286649599</v>
+      </c>
+      <c r="D181">
+        <v>23.6105440217206</v>
+      </c>
+      <c r="E181">
+        <f>C181/24/365+70</f>
+        <v>70.041360504893433</v>
+      </c>
+      <c r="F181">
+        <f>D181</f>
+        <v>23.6105440217206</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A182" t="s">
+        <v>3</v>
+      </c>
+      <c r="B182" t="s">
+        <v>10</v>
+      </c>
+      <c r="C182">
+        <v>370.55256566057301</v>
+      </c>
+      <c r="D182">
+        <v>23.033464405649401</v>
+      </c>
+      <c r="E182">
+        <f>C182/24/365+70</f>
+        <v>70.042300521194136</v>
+      </c>
+      <c r="F182">
+        <f>D182</f>
+        <v>23.033464405649401</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A183" t="s">
+        <v>3</v>
+      </c>
+      <c r="B183" t="s">
+        <v>10</v>
+      </c>
+      <c r="C183">
+        <v>382.25428436794698</v>
+      </c>
+      <c r="D183">
+        <v>22.181354953055902</v>
+      </c>
+      <c r="E183">
+        <f>C183/24/365+70</f>
+        <v>70.043636333831955</v>
+      </c>
+      <c r="F183">
+        <f>D183</f>
+        <v>22.181354953055902</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A184" t="s">
+        <v>3</v>
+      </c>
+      <c r="B184" t="s">
+        <v>10</v>
+      </c>
+      <c r="C184">
+        <v>390.05543017286197</v>
+      </c>
+      <c r="D184">
+        <v>21.710378510815499</v>
+      </c>
+      <c r="E184">
+        <f>C184/24/365+70</f>
+        <v>70.044526875590506</v>
+      </c>
+      <c r="F184">
+        <f>D184</f>
+        <v>21.710378510815499</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A185" t="s">
+        <v>3</v>
+      </c>
+      <c r="B185" t="s">
+        <v>10</v>
+      </c>
+      <c r="C185">
+        <v>401.32375189107302</v>
+      </c>
+      <c r="D185">
+        <v>20.890687494338099</v>
+      </c>
+      <c r="E185">
+        <f>C185/24/365+70</f>
+        <v>70.045813213686202</v>
+      </c>
+      <c r="F185">
+        <f>D185</f>
+        <v>20.890687494338099</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A186" t="s">
+        <v>3</v>
+      </c>
+      <c r="B186" t="s">
+        <v>10</v>
+      </c>
+      <c r="C186">
+        <v>409.12489769598898</v>
+      </c>
+      <c r="D186">
+        <v>20.414811544868499</v>
+      </c>
+      <c r="E186">
+        <f>C186/24/365+70</f>
+        <v>70.046703755444753</v>
+      </c>
+      <c r="F186">
+        <f>D186</f>
+        <v>20.414811544868499</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A187" t="s">
+        <v>3</v>
+      </c>
+      <c r="B187" t="s">
+        <v>10</v>
+      </c>
+      <c r="C187">
+        <v>421.260013392524</v>
+      </c>
+      <c r="D187">
+        <v>19.626136276190401</v>
+      </c>
+      <c r="E187">
+        <f>C187/24/365+70</f>
+        <v>70.048089042624724</v>
+      </c>
+      <c r="F187">
+        <f>D187</f>
+        <v>19.626136276190401</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A188" t="s">
+        <v>3</v>
+      </c>
+      <c r="B188" t="s">
+        <v>10</v>
+      </c>
+      <c r="C188">
+        <v>429.68029775338601</v>
+      </c>
+      <c r="D188">
+        <v>19.1472761391211</v>
+      </c>
+      <c r="E188">
+        <f>C188/24/365+70</f>
+        <v>70.049050262300611</v>
+      </c>
+      <c r="F188">
+        <f>D188</f>
+        <v>19.1472761391211</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A189" t="s">
+        <v>3</v>
+      </c>
+      <c r="B189" t="s">
+        <v>10</v>
+      </c>
+      <c r="C189">
+        <v>440.329480915651</v>
+      </c>
+      <c r="D189">
+        <v>18.5314210958073</v>
+      </c>
+      <c r="E189">
+        <f>C189/24/365+70</f>
+        <v>70.050265922478957</v>
+      </c>
+      <c r="F189">
+        <f>D189</f>
+        <v>18.5314210958073</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A190" t="s">
+        <v>3</v>
+      </c>
+      <c r="B190" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190">
+        <v>448.13062672056702</v>
+      </c>
+      <c r="D190">
+        <v>18.100479547268399</v>
+      </c>
+      <c r="E190">
+        <f>C190/24/365+70</f>
+        <v>70.051156464237508</v>
+      </c>
+      <c r="F190">
+        <f>D190</f>
+        <v>18.100479547268399</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A191" t="s">
+        <v>3</v>
+      </c>
+      <c r="B191" t="s">
+        <v>10</v>
+      </c>
+      <c r="C191">
+        <v>460.26574241710199</v>
+      </c>
+      <c r="D191">
+        <v>17.365270333881401</v>
+      </c>
+      <c r="E191">
+        <f>C191/24/365+70</f>
+        <v>70.052541751417479</v>
+      </c>
+      <c r="F191">
+        <f>D191</f>
+        <v>17.365270333881401</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A192" t="s">
+        <v>3</v>
+      </c>
+      <c r="B192" t="s">
+        <v>10</v>
+      </c>
+      <c r="C192">
+        <v>468.82533295305097</v>
+      </c>
+      <c r="D192">
+        <v>16.948438653480601</v>
+      </c>
+      <c r="E192">
+        <f>C192/24/365+70</f>
+        <v>70.053518873624782</v>
+      </c>
+      <c r="F192">
+        <f>D192</f>
+        <v>16.948438653480601</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A193" t="s">
+        <v>3</v>
+      </c>
+      <c r="B193" t="s">
+        <v>10</v>
+      </c>
+      <c r="C193">
+        <v>479.33520994022899</v>
+      </c>
+      <c r="D193">
+        <v>16.354836598917402</v>
+      </c>
+      <c r="E193">
+        <f>C193/24/365+70</f>
+        <v>70.054718631271712</v>
+      </c>
+      <c r="F193">
+        <f>D193</f>
+        <v>16.354836598917402</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A194" t="s">
+        <v>3</v>
+      </c>
+      <c r="B194" t="s">
+        <v>10</v>
+      </c>
+      <c r="C194">
+        <v>487.13635574514501</v>
+      </c>
+      <c r="D194">
+        <v>16.069998071876999</v>
+      </c>
+      <c r="E194">
+        <f>C194/24/365+70</f>
+        <v>70.055609173030263</v>
+      </c>
+      <c r="F194">
+        <f>D194</f>
+        <v>16.069998071876999</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A195" t="s">
+        <v>3</v>
+      </c>
+      <c r="B195" t="s">
+        <v>10</v>
+      </c>
+      <c r="C195">
+        <v>499.27147144167998</v>
+      </c>
+      <c r="D195">
+        <v>15.3779356184778</v>
+      </c>
+      <c r="E195">
+        <f>C195/24/365+70</f>
+        <v>70.056994460210234</v>
+      </c>
+      <c r="F195">
+        <f>D195</f>
+        <v>15.3779356184778</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A196" t="s">
+        <v>3</v>
+      </c>
+      <c r="B196" t="s">
+        <v>10</v>
+      </c>
+      <c r="C196">
+        <v>507.83106197762902</v>
+      </c>
+      <c r="D196">
+        <v>15.0471911957638</v>
+      </c>
+      <c r="E196">
+        <f>C196/24/365+70</f>
+        <v>70.057971582417537</v>
+      </c>
+      <c r="F196">
+        <f>D196</f>
+        <v>15.0471911957638</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A197" t="s">
+        <v>3</v>
+      </c>
+      <c r="B197" t="s">
+        <v>10</v>
+      </c>
+      <c r="C197">
+        <v>518.34093896480704</v>
+      </c>
+      <c r="D197">
+        <v>14.5201784253351</v>
+      </c>
+      <c r="E197">
+        <f>C197/24/365+70</f>
+        <v>70.059171340064481</v>
+      </c>
+      <c r="F197">
+        <f>D197</f>
+        <v>14.5201784253351</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A198" t="s">
+        <v>3</v>
+      </c>
+      <c r="B198" t="s">
+        <v>10</v>
+      </c>
+      <c r="C198">
+        <v>526.14208476972203</v>
+      </c>
+      <c r="D198">
+        <v>14.153222752386201</v>
+      </c>
+      <c r="E198">
+        <f>C198/24/365+70</f>
+        <v>70.060061881823032</v>
+      </c>
+      <c r="F198">
+        <f>D198</f>
+        <v>14.153222752386201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A199" t="s">
+        <v>3</v>
+      </c>
+      <c r="B199" t="s">
+        <v>10</v>
+      </c>
+      <c r="C199">
+        <v>537.41040648793398</v>
+      </c>
+      <c r="D199">
+        <v>13.6287996991942</v>
+      </c>
+      <c r="E199">
+        <f>C199/24/365+70</f>
+        <v>70.061348219918713</v>
+      </c>
+      <c r="F199">
+        <f>D199</f>
+        <v>13.6287996991942</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A200" t="s">
+        <v>3</v>
+      </c>
+      <c r="B200" t="s">
+        <v>10</v>
+      </c>
+      <c r="C200">
+        <v>545.21155229284898</v>
+      </c>
+      <c r="D200">
+        <v>13.380041878350101</v>
+      </c>
+      <c r="E200">
+        <f>C200/24/365+70</f>
+        <v>70.062238761677264</v>
+      </c>
+      <c r="F200">
+        <f>D200</f>
+        <v>13.380041878350101</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A201" t="s">
+        <v>3</v>
+      </c>
+      <c r="B201" t="s">
+        <v>10</v>
+      </c>
+      <c r="C201">
+        <v>557.34666798938497</v>
+      </c>
+      <c r="D201">
+        <v>12.825644233301601</v>
+      </c>
+      <c r="E201">
+        <f>C201/24/365+70</f>
+        <v>70.063624048857235</v>
+      </c>
+      <c r="F201">
+        <f>D201</f>
+        <v>12.825644233301601</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A202" t="s">
+        <v>3</v>
+      </c>
+      <c r="B202" t="s">
+        <v>10</v>
+      </c>
+      <c r="C202">
+        <v>565.58121078346198</v>
+      </c>
+      <c r="D202">
+        <v>12.5281540782414</v>
+      </c>
+      <c r="E202">
+        <f>C202/24/365+70</f>
+        <v>70.064564065157924</v>
+      </c>
+      <c r="F202">
+        <f>D202</f>
+        <v>12.5281540782414</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A203" t="s">
+        <v>3</v>
+      </c>
+      <c r="B203" t="s">
+        <v>10</v>
+      </c>
+      <c r="C203">
+        <v>577.28292949083504</v>
+      </c>
+      <c r="D203">
+        <v>12.0595476507707</v>
+      </c>
+      <c r="E203">
+        <f>C203/24/365+70</f>
+        <v>70.065899877795758</v>
+      </c>
+      <c r="F203">
+        <f>D203</f>
+        <v>12.0595476507707</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A204" t="s">
+        <v>3</v>
+      </c>
+      <c r="B204" t="s">
+        <v>10</v>
+      </c>
+      <c r="C204">
+        <v>585.08407529575095</v>
+      </c>
+      <c r="D204">
+        <v>11.784839186052199</v>
+      </c>
+      <c r="E204">
+        <f>C204/24/365+70</f>
+        <v>70.066790419554309</v>
+      </c>
+      <c r="F204">
+        <f>D204</f>
+        <v>11.784839186052199</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A205" t="s">
+        <v>3</v>
+      </c>
+      <c r="B205" t="s">
+        <v>10</v>
+      </c>
+      <c r="C205">
+        <v>596.35239701396199</v>
+      </c>
+      <c r="D205">
+        <v>11.3481724667154</v>
+      </c>
+      <c r="E205">
+        <f>C205/24/365+70</f>
+        <v>70.06807675764999</v>
+      </c>
+      <c r="F205">
+        <f>D205</f>
+        <v>11.3481724667154</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A206" t="s">
+        <v>3</v>
+      </c>
+      <c r="B206" t="s">
+        <v>10</v>
+      </c>
+      <c r="C206">
+        <v>604.27737053006695</v>
+      </c>
+      <c r="D206">
+        <v>11.09651203002</v>
+      </c>
+      <c r="E206">
+        <f>C206/24/365+70</f>
+        <v>70.068981434992011</v>
+      </c>
+      <c r="F206">
+        <f>D206</f>
+        <v>11.09651203002</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A207" t="s">
+        <v>3</v>
+      </c>
+      <c r="B207" t="s">
+        <v>10</v>
+      </c>
+      <c r="C207">
+        <v>616.28865851541298</v>
+      </c>
+      <c r="D207">
+        <v>10.6703276749389</v>
+      </c>
+      <c r="E207">
+        <f>C207/24/365+70</f>
+        <v>70.070352586588513</v>
+      </c>
+      <c r="F207">
+        <f>D207</f>
+        <v>10.6703276749389</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A208" t="s">
+        <v>3</v>
+      </c>
+      <c r="B208" t="s">
+        <v>10</v>
+      </c>
+      <c r="C208">
+        <v>624.08980432032899</v>
+      </c>
+      <c r="D208">
+        <v>10.434876868222799</v>
+      </c>
+      <c r="E208">
+        <f>C208/24/365+70</f>
+        <v>70.071243128347064</v>
+      </c>
+      <c r="F208">
+        <f>D208</f>
+        <v>10.434876868222799</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A209" t="s">
+        <v>3</v>
+      </c>
+      <c r="B209" t="s">
+        <v>10</v>
+      </c>
+      <c r="C209">
+        <v>635.35812603854004</v>
+      </c>
+      <c r="D209">
+        <v>10.049452857640899</v>
+      </c>
+      <c r="E209">
+        <f>C209/24/365+70</f>
+        <v>70.072529466442759</v>
+      </c>
+      <c r="F209">
+        <f>D209</f>
+        <v>10.049452857640899</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A210" t="s">
+        <v>3</v>
+      </c>
+      <c r="B210" t="s">
+        <v>10</v>
+      </c>
+      <c r="C210">
+        <v>643.91771657448896</v>
+      </c>
+      <c r="D210">
+        <v>9.8176271492764506</v>
+      </c>
+      <c r="E210">
+        <f>C210/24/365+70</f>
+        <v>70.073506588650062</v>
+      </c>
+      <c r="F210">
+        <f>D210</f>
+        <v>9.8176271492764506</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A211" t="s">
+        <v>3</v>
+      </c>
+      <c r="B211" t="s">
+        <v>10</v>
+      </c>
+      <c r="C211">
+        <v>654.42759356166698</v>
+      </c>
+      <c r="D211">
+        <v>9.4727664376333802</v>
+      </c>
+      <c r="E211">
+        <f>C211/24/365+70</f>
+        <v>70.074706346296992</v>
+      </c>
+      <c r="F211">
+        <f>D211</f>
+        <v>9.4727664376333802</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A212" t="s">
+        <v>3</v>
+      </c>
+      <c r="B212" t="s">
+        <v>10</v>
+      </c>
+      <c r="C212">
+        <v>663.09553334490602</v>
+      </c>
+      <c r="D212">
+        <v>9.2491732641410191</v>
+      </c>
+      <c r="E212">
+        <f>C212/24/365+70</f>
+        <v>70.075695837139833</v>
+      </c>
+      <c r="F212">
+        <f>D212</f>
+        <v>9.2491732641410191</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A213" t="s">
+        <v>3</v>
+      </c>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>49.233107779683401</v>
+      </c>
+      <c r="E213">
+        <f>C213/24/365+70</f>
+        <v>70</v>
+      </c>
+      <c r="F213">
+        <f>D213</f>
+        <v>49.233107779683401</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A214" t="s">
+        <v>3</v>
+      </c>
+      <c r="B214" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214">
+        <v>14.7540983606556</v>
+      </c>
+      <c r="D214">
+        <v>37.122250765361898</v>
+      </c>
+      <c r="E214">
+        <f>C214/24/365+70</f>
+        <v>70.001684257803731</v>
+      </c>
+      <c r="F214">
+        <f>D214</f>
+        <v>37.122250765361898</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A215" t="s">
+        <v>3</v>
+      </c>
+      <c r="B215" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215">
+        <v>23.401577341831601</v>
+      </c>
+      <c r="D215">
+        <v>32.930898543452003</v>
+      </c>
+      <c r="E215">
+        <f>C215/24/365+70</f>
+        <v>70.002671412938568</v>
+      </c>
+      <c r="F215">
+        <f>D215</f>
+        <v>32.930898543452003</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A216" t="s">
+        <v>3</v>
+      </c>
+      <c r="B216" t="s">
+        <v>11</v>
+      </c>
+      <c r="C216">
+        <v>32.936311103395099</v>
+      </c>
+      <c r="D216">
+        <v>29.225505198875901</v>
+      </c>
+      <c r="E216">
+        <f>C216/24/365+70</f>
+        <v>70.003759852865684</v>
+      </c>
+      <c r="F216">
+        <f>D216</f>
+        <v>29.225505198875901</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A217" t="s">
+        <v>3</v>
+      </c>
+      <c r="B217" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217">
+        <v>42.4710448649586</v>
+      </c>
+      <c r="D217">
+        <v>26.315173954349302</v>
+      </c>
+      <c r="E217">
+        <f>C217/24/365+70</f>
+        <v>70.004848292792801</v>
+      </c>
+      <c r="F217">
+        <f>D217</f>
+        <v>26.315173954349302</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A218" t="s">
+        <v>3</v>
+      </c>
+      <c r="B218" t="s">
+        <v>11</v>
+      </c>
+      <c r="C218">
+        <v>52.005778626521902</v>
+      </c>
+      <c r="D218">
+        <v>23.999198199822501</v>
+      </c>
+      <c r="E218">
+        <f>C218/24/365+70</f>
+        <v>70.005936732719917</v>
+      </c>
+      <c r="F218">
+        <f>D218</f>
+        <v>23.999198199822501</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A219" t="s">
+        <v>3</v>
+      </c>
+      <c r="B219" t="s">
+        <v>11</v>
+      </c>
+      <c r="C219">
+        <v>60.866339293833498</v>
+      </c>
+      <c r="D219">
+        <v>22.144242398380101</v>
+      </c>
+      <c r="E219">
+        <f>C219/24/365+70</f>
+        <v>70.006948212248147</v>
+      </c>
+      <c r="F219">
+        <f>D219</f>
+        <v>22.144242398380101</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A220" t="s">
+        <v>3</v>
+      </c>
+      <c r="B220" t="s">
+        <v>11</v>
+      </c>
+      <c r="C220">
+        <v>70.401073055396793</v>
+      </c>
+      <c r="D220">
+        <v>20.5596676877154</v>
+      </c>
+      <c r="E220">
+        <f>C220/24/365+70</f>
+        <v>70.008036652175278</v>
+      </c>
+      <c r="F220">
+        <f>D220</f>
+        <v>20.5596676877154</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A221" t="s">
+        <v>3</v>
+      </c>
+      <c r="B221" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221">
+        <v>79.935806816960394</v>
+      </c>
+      <c r="D221">
+        <v>19.308229633506301</v>
+      </c>
+      <c r="E221">
+        <f>C221/24/365+70</f>
+        <v>70.009125092102394</v>
+      </c>
+      <c r="F221">
+        <f>D221</f>
+        <v>19.308229633506301</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A222" t="s">
+        <v>3</v>
+      </c>
+      <c r="B222" t="s">
+        <v>11</v>
+      </c>
+      <c r="C222">
+        <v>89.277919694451796</v>
+      </c>
+      <c r="D222">
+        <v>18.267655393465802</v>
+      </c>
+      <c r="E222">
+        <f>C222/24/365+70</f>
+        <v>70.010191543344121</v>
+      </c>
+      <c r="F222">
+        <f>D222</f>
+        <v>18.267655393465802</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A223" t="s">
+        <v>3</v>
+      </c>
+      <c r="B223" t="s">
+        <v>11</v>
+      </c>
+      <c r="C223">
+        <v>100.54624141266299</v>
+      </c>
+      <c r="D223">
+        <v>17.263050286711199</v>
+      </c>
+      <c r="E223">
+        <f>C223/24/365+70</f>
+        <v>70.011477881439802</v>
+      </c>
+      <c r="F223">
+        <f>D223</f>
+        <v>17.263050286711199</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A224" t="s">
+        <v>3</v>
+      </c>
+      <c r="B224" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224">
+        <v>110.94776915254999</v>
+      </c>
+      <c r="D224">
+        <v>16.3735651484401</v>
+      </c>
+      <c r="E224">
+        <f>C224/24/365+70</f>
+        <v>70.012665270451208</v>
+      </c>
+      <c r="F224">
+        <f>D224</f>
+        <v>16.3735651484401</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A225" t="s">
+        <v>3</v>
+      </c>
+      <c r="B225" t="s">
+        <v>11</v>
+      </c>
+      <c r="C225">
+        <v>123.73298033282801</v>
+      </c>
+      <c r="D225">
+        <v>15.5077584983003</v>
+      </c>
+      <c r="E225">
+        <f>C225/24/365+70</f>
+        <v>70.014124769444393</v>
+      </c>
+      <c r="F225">
+        <f>D225</f>
+        <v>15.5077584983003</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A226" t="s">
+        <v>3</v>
+      </c>
+      <c r="B226" t="s">
+        <v>11</v>
+      </c>
+      <c r="C226">
+        <v>132.98910174421599</v>
+      </c>
+      <c r="D226">
+        <v>14.914908395968601</v>
+      </c>
+      <c r="E226">
+        <f>C226/24/365+70</f>
+        <v>70.015181404308706</v>
+      </c>
+      <c r="F226">
+        <f>D226</f>
+        <v>14.914908395968601</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A227" t="s">
+        <v>3</v>
+      </c>
+      <c r="B227" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227">
+        <v>141.17720914659799</v>
+      </c>
+      <c r="D227">
+        <v>14.4061410367093</v>
+      </c>
+      <c r="E227">
+        <f>C227/24/365+70</f>
+        <v>70.016116119765599</v>
+      </c>
+      <c r="F227">
+        <f>D227</f>
+        <v>14.4061410367093</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A228" t="s">
+        <v>3</v>
+      </c>
+      <c r="B228" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228">
+        <v>153.29684637923501</v>
+      </c>
+      <c r="D228">
+        <v>13.7658217922445</v>
+      </c>
+      <c r="E228">
+        <f>C228/24/365+70</f>
+        <v>70.017499639997624</v>
+      </c>
+      <c r="F228">
+        <f>D228</f>
+        <v>13.7658217922445</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A229" t="s">
+        <v>3</v>
+      </c>
+      <c r="B229" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229">
+        <v>161.98026462637301</v>
+      </c>
+      <c r="D229">
+        <v>13.4173410734955</v>
+      </c>
+      <c r="E229">
+        <f>C229/24/365+70</f>
+        <v>70.018490897788396</v>
+      </c>
+      <c r="F229">
+        <f>D229</f>
+        <v>13.4173410734955</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A230" t="s">
+        <v>3</v>
+      </c>
+      <c r="B230" t="s">
+        <v>11</v>
+      </c>
+      <c r="C230">
+        <v>172.750179807048</v>
+      </c>
+      <c r="D230">
+        <v>12.894571801535101</v>
+      </c>
+      <c r="E230">
+        <f>C230/24/365+70</f>
+        <v>70.019720340160617</v>
+      </c>
+      <c r="F230">
+        <f>D230</f>
+        <v>12.894571801535101</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A231" t="s">
+        <v>3</v>
+      </c>
+      <c r="B231" t="s">
+        <v>11</v>
+      </c>
+      <c r="C231">
+        <v>181.405736819168</v>
+      </c>
+      <c r="D231">
+        <v>12.476397495177199</v>
+      </c>
+      <c r="E231">
+        <f>C231/24/365+70</f>
+        <v>70.020708417445107</v>
+      </c>
+      <c r="F231">
+        <f>D231</f>
+        <v>12.476397495177199</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A232" t="s">
+        <v>3</v>
+      </c>
+      <c r="B232" t="s">
+        <v>11</v>
+      </c>
+      <c r="C232">
+        <v>193.29319709332501</v>
+      </c>
+      <c r="D232">
+        <v>11.9781564121367</v>
+      </c>
+      <c r="E232">
+        <f>C232/24/365+70</f>
+        <v>70.022065433458138</v>
+      </c>
+      <c r="F232">
+        <f>D232</f>
+        <v>11.9781564121367</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A233" t="s">
+        <v>3</v>
+      </c>
+      <c r="B233" t="s">
+        <v>11</v>
+      </c>
+      <c r="C233">
+        <v>202.53899952878101</v>
+      </c>
+      <c r="D233">
+        <v>11.6848464906071</v>
+      </c>
+      <c r="E233">
+        <f>C233/24/365+70</f>
+        <v>70.023120890357163</v>
+      </c>
+      <c r="F233">
+        <f>D233</f>
+        <v>11.6848464906071</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A234" t="s">
+        <v>3</v>
+      </c>
+      <c r="B234" t="s">
+        <v>11</v>
+      </c>
+      <c r="C234">
+        <v>212.36266461645201</v>
+      </c>
+      <c r="D234">
+        <v>11.2907916135294</v>
+      </c>
+      <c r="E234">
+        <f>C234/24/365+70</f>
+        <v>70.024242313312385</v>
+      </c>
+      <c r="F234">
+        <f>D234</f>
+        <v>11.2907916135294</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A235" t="s">
+        <v>3</v>
+      </c>
+      <c r="B235" t="s">
+        <v>11</v>
+      </c>
+      <c r="C235">
+        <v>220.163810421368</v>
+      </c>
+      <c r="D235">
+        <v>10.977041892507099</v>
+      </c>
+      <c r="E235">
+        <f>C235/24/365+70</f>
+        <v>70.025132855070936</v>
+      </c>
+      <c r="F235">
+        <f>D235</f>
+        <v>10.977041892507099</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A236" t="s">
+        <v>3</v>
+      </c>
+      <c r="B236" t="s">
+        <v>11</v>
+      </c>
+      <c r="C236">
+        <v>231.43213213957901</v>
+      </c>
+      <c r="D236">
+        <v>10.6610089194763</v>
+      </c>
+      <c r="E236">
+        <f>C236/24/365+70</f>
+        <v>70.026419193166618</v>
+      </c>
+      <c r="F236">
+        <f>D236</f>
+        <v>10.6610089194763</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A237" t="s">
+        <v>3</v>
+      </c>
+      <c r="B237" t="s">
+        <v>11</v>
+      </c>
+      <c r="C237">
+        <v>240.44678951414801</v>
+      </c>
+      <c r="D237">
+        <v>10.3581521626541</v>
+      </c>
+      <c r="E237">
+        <f>C237/24/365+70</f>
+        <v>70.027448263643166</v>
+      </c>
+      <c r="F237">
+        <f>D237</f>
+        <v>10.3581521626541</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A238" t="s">
+        <v>3</v>
+      </c>
+      <c r="B238" t="s">
+        <v>11</v>
+      </c>
+      <c r="C238">
+        <v>250.50159966270601</v>
+      </c>
+      <c r="D238">
+        <v>9.9725209503053005</v>
+      </c>
+      <c r="E238">
+        <f>C238/24/365+70</f>
+        <v>70.02859607302085</v>
+      </c>
+      <c r="F238">
+        <f>D238</f>
+        <v>9.9725209503053005</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A239" t="s">
+        <v>3</v>
+      </c>
+      <c r="B239" t="s">
+        <v>11</v>
+      </c>
+      <c r="C239">
+        <v>260.686428908013</v>
+      </c>
+      <c r="D239">
+        <v>9.7011698135891695</v>
+      </c>
+      <c r="E239">
+        <f>C239/24/365+70</f>
+        <v>70.029758724761194</v>
+      </c>
+      <c r="F239">
+        <f>D239</f>
+        <v>9.7011698135891695</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A240" t="s">
+        <v>3</v>
+      </c>
+      <c r="B240" t="s">
+        <v>11</v>
+      </c>
+      <c r="C240">
+        <v>269.07575634107599</v>
+      </c>
+      <c r="D240">
+        <v>9.4411675966640001</v>
+      </c>
+      <c r="E240">
+        <f>C240/24/365+70</f>
+        <v>70.030716410541217</v>
+      </c>
+      <c r="F240">
+        <f>D240</f>
+        <v>9.4411675966640001</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A241" t="s">
+        <v>3</v>
+      </c>
+      <c r="B241" t="s">
+        <v>11</v>
+      </c>
+      <c r="C241">
+        <v>277.37221299074901</v>
+      </c>
+      <c r="D241">
+        <v>9.2219402438512397</v>
+      </c>
+      <c r="E241">
+        <f>C241/24/365+70</f>
+        <v>70.031663494633648</v>
+      </c>
+      <c r="F241">
+        <f>D241</f>
+        <v>9.2219402438512397</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A242" t="s">
+        <v>3</v>
+      </c>
+      <c r="B242" t="s">
+        <v>11</v>
+      </c>
+      <c r="C242">
+        <v>289.50732868728397</v>
+      </c>
+      <c r="D242">
+        <v>8.8538202551293494</v>
+      </c>
+      <c r="E242">
+        <f>C242/24/365+70</f>
+        <v>70.033048781813619</v>
+      </c>
+      <c r="F242">
+        <f>D242</f>
+        <v>8.8538202551293494</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A243" t="s">
+        <v>3</v>
+      </c>
+      <c r="B243" t="s">
+        <v>11</v>
+      </c>
+      <c r="C243">
+        <v>299.61992510106302</v>
+      </c>
+      <c r="D243">
+        <v>8.4993491524009706</v>
+      </c>
+      <c r="E243">
+        <f>C243/24/365+70</f>
+        <v>70.034203187796919</v>
+      </c>
+      <c r="F243">
+        <f>D243</f>
+        <v>8.4993491524009706</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A244" t="s">
+        <v>3</v>
+      </c>
+      <c r="B244" t="s">
+        <v>11</v>
+      </c>
+      <c r="C244">
+        <v>308.57679621041098</v>
+      </c>
+      <c r="D244">
+        <v>8.2961549354371709</v>
+      </c>
+      <c r="E244">
+        <f>C244/24/365+70</f>
+        <v>70.035225661667852</v>
+      </c>
+      <c r="F244">
+        <f>D244</f>
+        <v>8.2961549354371709</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A245" t="s">
+        <v>3</v>
+      </c>
+      <c r="B245" t="s">
+        <v>11</v>
+      </c>
+      <c r="C245">
+        <v>321.03695964881803</v>
+      </c>
+      <c r="D245">
+        <v>8.0126635843499301</v>
+      </c>
+      <c r="E245">
+        <f>C245/24/365+70</f>
+        <v>70.036648054754437</v>
+      </c>
+      <c r="F245">
+        <f>D245</f>
+        <v>8.0126635843499301</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A246" t="s">
+        <v>3</v>
+      </c>
+      <c r="B246" t="s">
+        <v>11</v>
+      </c>
+      <c r="C246">
+        <v>329.81324867934802</v>
+      </c>
+      <c r="D246">
+        <v>7.8119650382236596</v>
+      </c>
+      <c r="E246">
+        <f>C246/24/365+70</f>
+        <v>70.037649914232802</v>
+      </c>
+      <c r="F246">
+        <f>D246</f>
+        <v>7.8119650382236596</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A247" t="s">
+        <v>3</v>
+      </c>
+      <c r="B247" t="s">
+        <v>11</v>
+      </c>
+      <c r="C247">
+        <v>342.67069269115302</v>
+      </c>
+      <c r="D247">
+        <v>7.4660472708685903</v>
+      </c>
+      <c r="E247">
+        <f>C247/24/365+70</f>
+        <v>70.039117658983002</v>
+      </c>
+      <c r="F247">
+        <f>D247</f>
+        <v>7.4660472708685903</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A248" t="s">
+        <v>3</v>
+      </c>
+      <c r="B248" t="s">
+        <v>11</v>
+      </c>
+      <c r="C248">
+        <v>350.94135190099399</v>
+      </c>
+      <c r="D248">
+        <v>7.3289409017193297</v>
+      </c>
+      <c r="E248">
+        <f>C248/24/365+70</f>
+        <v>70.040061798162213</v>
+      </c>
+      <c r="F248">
+        <f>D248</f>
+        <v>7.3289409017193297</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A249" t="s">
+        <v>3</v>
+      </c>
+      <c r="B249" t="s">
+        <v>11</v>
+      </c>
+      <c r="C249">
+        <v>362.10132437191498</v>
+      </c>
+      <c r="D249">
+        <v>7.0320494362759201</v>
+      </c>
+      <c r="E249">
+        <f>C249/24/365+70</f>
+        <v>70.041335767622371</v>
+      </c>
+      <c r="F249">
+        <f>D249</f>
+        <v>7.0320494362759201</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A250" t="s">
+        <v>3</v>
+      </c>
+      <c r="B250" t="s">
+        <v>11</v>
+      </c>
+      <c r="C250">
+        <v>370.98596264973497</v>
+      </c>
+      <c r="D250">
+        <v>6.8568412324591899</v>
+      </c>
+      <c r="E250">
+        <f>C250/24/365+70</f>
+        <v>70.042349995736274</v>
+      </c>
+      <c r="F250">
+        <f>D250</f>
+        <v>6.8568412324591899</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A251" t="s">
+        <v>3</v>
+      </c>
+      <c r="B251" t="s">
+        <v>11</v>
+      </c>
+      <c r="C251">
+        <v>380.52069641129901</v>
+      </c>
+      <c r="D251">
+        <v>6.6770623121115804</v>
+      </c>
+      <c r="E251">
+        <f>C251/24/365+70</f>
+        <v>70.04343843566339</v>
+      </c>
+      <c r="F251">
+        <f>D251</f>
+        <v>6.6770623121115804</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A252" t="s">
+        <v>3</v>
+      </c>
+      <c r="B252" t="s">
+        <v>11</v>
+      </c>
+      <c r="C252">
+        <v>390.05543017286197</v>
+      </c>
+      <c r="D252">
+        <v>6.4854111056639896</v>
+      </c>
+      <c r="E252">
+        <f>C252/24/365+70</f>
+        <v>70.044526875590506</v>
+      </c>
+      <c r="F252">
+        <f>D252</f>
+        <v>6.4854111056639896</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A253" t="s">
+        <v>3</v>
+      </c>
+      <c r="B253" t="s">
+        <v>11</v>
+      </c>
+      <c r="C253">
+        <v>399.837819356804</v>
+      </c>
+      <c r="D253">
+        <v>6.2436886059985204</v>
+      </c>
+      <c r="E253">
+        <f>C253/24/365+70</f>
+        <v>70.045643586684562</v>
+      </c>
+      <c r="F253">
+        <f>D253</f>
+        <v>6.2436886059985204</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A254" t="s">
+        <v>3</v>
+      </c>
+      <c r="B254" t="s">
+        <v>11</v>
+      </c>
+      <c r="C254">
+        <v>407.82470672850297</v>
+      </c>
+      <c r="D254">
+        <v>6.1446428309116197</v>
+      </c>
+      <c r="E254">
+        <f>C254/24/365+70</f>
+        <v>70.046555331818325</v>
+      </c>
+      <c r="F254">
+        <f>D254</f>
+        <v>6.1446428309116197</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A255" t="s">
+        <v>3</v>
+      </c>
+      <c r="B255" t="s">
+        <v>11</v>
+      </c>
+      <c r="C255">
+        <v>419.81535676198399</v>
+      </c>
+      <c r="D255">
+        <v>5.8540437094445599</v>
+      </c>
+      <c r="E255">
+        <f>C255/24/365+70</f>
+        <v>70.047924127484251</v>
+      </c>
+      <c r="F255">
+        <f>D255</f>
+        <v>5.8540437094445599</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A256" t="s">
+        <v>3</v>
+      </c>
+      <c r="B256" t="s">
+        <v>11</v>
+      </c>
+      <c r="C256">
+        <v>427.327571240792</v>
+      </c>
+      <c r="D256">
+        <v>5.7118462490692599</v>
+      </c>
+      <c r="E256">
+        <f>C256/24/365+70</f>
+        <v>70.048781686214696</v>
+      </c>
+      <c r="F256">
+        <f>D256</f>
+        <v>5.7118462490692599</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A257" t="s">
+        <v>3</v>
+      </c>
+      <c r="B257" t="s">
+        <v>11</v>
+      </c>
+      <c r="C257">
+        <v>441.19627489397499</v>
+      </c>
+      <c r="D257">
+        <v>5.4618819864493897</v>
+      </c>
+      <c r="E257">
+        <f>C257/24/365+70</f>
+        <v>70.050364871563232</v>
+      </c>
+      <c r="F257">
+        <f>D257</f>
+        <v>5.4618819864493897</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A258" t="s">
+        <v>3</v>
+      </c>
+      <c r="B258" t="s">
+        <v>11</v>
+      </c>
+      <c r="C258">
+        <v>449.49273154364698</v>
+      </c>
+      <c r="D258">
+        <v>5.3649873577667897</v>
+      </c>
+      <c r="E258">
+        <f>C258/24/365+70</f>
+        <v>70.051311955655663</v>
+      </c>
+      <c r="F258">
+        <f>D258</f>
+        <v>5.3649873577667897</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A259" t="s">
+        <v>3</v>
+      </c>
+      <c r="B259" t="s">
+        <v>11</v>
+      </c>
+      <c r="C259">
+        <v>460.61246000843198</v>
+      </c>
+      <c r="D259">
+        <v>5.1828835668930697</v>
+      </c>
+      <c r="E259">
+        <f>C259/24/365+70</f>
+        <v>70.052581331051186</v>
+      </c>
+      <c r="F259">
+        <f>D259</f>
+        <v>5.1828835668930697</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A260" t="s">
+        <v>3</v>
+      </c>
+      <c r="B260" t="s">
+        <v>11</v>
+      </c>
+      <c r="C260">
+        <v>469.150380694923</v>
+      </c>
+      <c r="D260">
+        <v>5.0399821979419901</v>
+      </c>
+      <c r="E260">
+        <f>C260/24/365+70</f>
+        <v>70.053555979531382</v>
+      </c>
+      <c r="F260">
+        <f>D260</f>
+        <v>5.0399821979419901</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A261" t="s">
+        <v>3</v>
+      </c>
+      <c r="B261" t="s">
+        <v>11</v>
+      </c>
+      <c r="C261">
+        <v>479.95434849617499</v>
+      </c>
+      <c r="D261">
+        <v>4.8632674560537197</v>
+      </c>
+      <c r="E261">
+        <f>C261/24/365+70</f>
+        <v>70.054789309189061</v>
+      </c>
+      <c r="F261">
+        <f>D261</f>
+        <v>4.8632674560537197</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A262" t="s">
+        <v>3</v>
+      </c>
+      <c r="B262" t="s">
+        <v>11</v>
+      </c>
+      <c r="C262">
+        <v>488.86994370179201</v>
+      </c>
+      <c r="D262">
+        <v>4.7459289085727496</v>
+      </c>
+      <c r="E262">
+        <f>C262/24/365+70</f>
+        <v>70.055807071198828</v>
+      </c>
+      <c r="F262">
+        <f>D262</f>
+        <v>4.7459289085727496</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A263" t="s">
+        <v>3</v>
+      </c>
+      <c r="B263" t="s">
+        <v>11</v>
+      </c>
+      <c r="C263">
+        <v>501.87185337665198</v>
+      </c>
+      <c r="D263">
+        <v>4.5407173568452297</v>
+      </c>
+      <c r="E263">
+        <f>C263/24/365+70</f>
+        <v>70.057291307463089</v>
+      </c>
+      <c r="F263">
+        <f>D263</f>
+        <v>4.5407173568452297</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A264" t="s">
+        <v>3</v>
+      </c>
+      <c r="B264" t="s">
+        <v>11</v>
+      </c>
+      <c r="C264">
+        <v>510.41596544870202</v>
+      </c>
+      <c r="D264">
+        <v>4.4261967898564896</v>
+      </c>
+      <c r="E264">
+        <f>C264/24/365+70</f>
+        <v>70.05826666272246</v>
+      </c>
+      <c r="F264">
+        <f>D264</f>
+        <v>4.4261967898564896</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A265" t="s">
+        <v>3</v>
+      </c>
+      <c r="B265" t="s">
+        <v>11</v>
+      </c>
+      <c r="C265">
+        <v>522.67490885642701</v>
+      </c>
+      <c r="D265">
+        <v>4.2733918779202398</v>
+      </c>
+      <c r="E265">
+        <f>C265/24/365+70</f>
+        <v>70.059666085485887</v>
+      </c>
+      <c r="F265">
+        <f>D265</f>
+        <v>4.2733918779202398</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A266" t="s">
+        <v>3</v>
+      </c>
+      <c r="B266" t="s">
+        <v>11</v>
+      </c>
+      <c r="C266">
+        <v>530.476054661342</v>
+      </c>
+      <c r="D266">
+        <v>4.1973063198010898</v>
+      </c>
+      <c r="E266">
+        <f>C266/24/365+70</f>
+        <v>70.060556627244452</v>
+      </c>
+      <c r="F266">
+        <f>D266</f>
+        <v>4.1973063198010898</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A267" t="s">
+        <v>3</v>
+      </c>
+      <c r="B267" t="s">
+        <v>11</v>
+      </c>
+      <c r="C267">
+        <v>541.74437637955305</v>
+      </c>
+      <c r="D267">
+        <v>4.0144691726000996</v>
+      </c>
+      <c r="E267">
+        <f>C267/24/365+70</f>
+        <v>70.061842965340134</v>
+      </c>
+      <c r="F267">
+        <f>D267</f>
+        <v>4.0144691726000996</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A268" t="s">
+        <v>3</v>
+      </c>
+      <c r="B268" t="s">
+        <v>11</v>
+      </c>
+      <c r="C268">
+        <v>551.65059327468396</v>
+      </c>
+      <c r="D268">
+        <v>3.9040903107451999</v>
+      </c>
+      <c r="E268">
+        <f>C268/24/365+70</f>
+        <v>70.06297381201766</v>
+      </c>
+      <c r="F268">
+        <f>D268</f>
+        <v>3.9040903107451999</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A269" t="s">
+        <v>3</v>
+      </c>
+      <c r="B269" t="s">
+        <v>11</v>
+      </c>
+      <c r="C269">
+        <v>560.48879616080899</v>
+      </c>
+      <c r="D269">
+        <v>3.79005769888651</v>
+      </c>
+      <c r="E269">
+        <f>C269/24/365+70</f>
+        <v>70.063982739287766</v>
+      </c>
+      <c r="F269">
+        <f>D269</f>
+        <v>3.79005769888651</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A270" t="s">
+        <v>3</v>
+      </c>
+      <c r="B270" t="s">
+        <v>11</v>
+      </c>
+      <c r="C270">
+        <v>570.34857766424398</v>
+      </c>
+      <c r="D270">
+        <v>3.6661089505277702</v>
+      </c>
+      <c r="E270">
+        <f>C270/24/365+70</f>
+        <v>70.065108285121482</v>
+      </c>
+      <c r="F270">
+        <f>D270</f>
+        <v>3.6661089505277702</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A271" t="s">
+        <v>3</v>
+      </c>
+      <c r="B271" t="s">
+        <v>11</v>
+      </c>
+      <c r="C271">
+        <v>579.88331142580705</v>
+      </c>
+      <c r="D271">
+        <v>3.5730282844434602</v>
+      </c>
+      <c r="E271">
+        <f>C271/24/365+70</f>
+        <v>70.066196725048613</v>
+      </c>
+      <c r="F271">
+        <f>D271</f>
+        <v>3.5730282844434602</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A272" t="s">
+        <v>3</v>
+      </c>
+      <c r="B272" t="s">
+        <v>11</v>
+      </c>
+      <c r="C272">
+        <v>589.17038976499202</v>
+      </c>
+      <c r="D272">
+        <v>3.4472733905631299</v>
+      </c>
+      <c r="E272">
+        <f>C272/24/365+70</f>
+        <v>70.067256893808789</v>
+      </c>
+      <c r="F272">
+        <f>D272</f>
+        <v>3.4472733905631299</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A273" t="s">
+        <v>3</v>
+      </c>
+      <c r="B273" t="s">
+        <v>11</v>
+      </c>
+      <c r="C273">
+        <v>600.68636690558196</v>
+      </c>
+      <c r="D273">
+        <v>3.3313283508826599</v>
+      </c>
+      <c r="E273">
+        <f>C273/24/365+70</f>
+        <v>70.068571503071411</v>
+      </c>
+      <c r="F273">
+        <f>D273</f>
+        <v>3.3313283508826599</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A274" t="s">
+        <v>3</v>
+      </c>
+      <c r="B274" t="s">
+        <v>11</v>
+      </c>
+      <c r="C274">
+        <v>609.70102428015105</v>
+      </c>
+      <c r="D274">
+        <v>3.25493094439849</v>
+      </c>
+      <c r="E274">
+        <f>C274/24/365+70</f>
+        <v>70.069600573547959</v>
+      </c>
+      <c r="F274">
+        <f>D274</f>
+        <v>3.25493094439849</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A275" t="s">
+        <v>3</v>
+      </c>
+      <c r="B275" t="s">
+        <v>11</v>
+      </c>
+      <c r="C275">
+        <v>619.75583442870902</v>
+      </c>
+      <c r="D275">
+        <v>3.1455120666568201</v>
+      </c>
+      <c r="E275">
+        <f>C275/24/365+70</f>
+        <v>70.070748382925657</v>
+      </c>
+      <c r="F275">
+        <f>D275</f>
+        <v>3.1455120666568201</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A276" t="s">
+        <v>3</v>
+      </c>
+      <c r="B276" t="s">
+        <v>11</v>
+      </c>
+      <c r="C276">
+        <v>628.42377421194897</v>
+      </c>
+      <c r="D276">
+        <v>3.0524391520929401</v>
+      </c>
+      <c r="E276">
+        <f>C276/24/365+70</f>
+        <v>70.071737873768484</v>
+      </c>
+      <c r="F276">
+        <f>D276</f>
+        <v>3.0524391520929401</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A277" t="s">
+        <v>3</v>
+      </c>
+      <c r="B277" t="s">
+        <v>11</v>
+      </c>
+      <c r="C277">
+        <v>638.82530195183597</v>
+      </c>
+      <c r="D277">
+        <v>2.9751219546292198</v>
+      </c>
+      <c r="E277">
+        <f>C277/24/365+70</f>
+        <v>70.07292526277989</v>
+      </c>
+      <c r="F277">
+        <f>D277</f>
+        <v>2.9751219546292198</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A278" t="s">
+        <v>3</v>
+      </c>
+      <c r="B278" t="s">
+        <v>11</v>
+      </c>
+      <c r="C278">
+        <v>646.62644775675199</v>
+      </c>
+      <c r="D278">
+        <v>2.89614518444967</v>
+      </c>
+      <c r="E278">
+        <f>C278/24/365+70</f>
+        <v>70.073815804538441</v>
+      </c>
+      <c r="F278">
+        <f>D278</f>
+        <v>2.89614518444967</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A279" t="s">
+        <v>3</v>
+      </c>
+      <c r="B279" t="s">
+        <v>11</v>
+      </c>
+      <c r="C279">
+        <v>657.89476947496303</v>
+      </c>
+      <c r="D279">
+        <v>2.79248229688204</v>
+      </c>
+      <c r="E279">
+        <f>C279/24/365+70</f>
+        <v>70.075102142634123</v>
+      </c>
+      <c r="F279">
+        <f>D279</f>
+        <v>2.79248229688204</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A280" t="s">
+        <v>3</v>
+      </c>
+      <c r="B280" t="s">
+        <v>11</v>
+      </c>
+      <c r="C280">
+        <v>666.81036468058096</v>
+      </c>
+      <c r="D280">
+        <v>2.7329621320613202</v>
+      </c>
+      <c r="E280">
+        <f>C280/24/365+70</f>
+        <v>70.076119904643903</v>
+      </c>
+      <c r="F280">
+        <f>D280</f>
+        <v>2.7329621320613202</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F49">
-    <sortCondition ref="E2:E49"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A95:F145">
+    <sortCondition ref="E95:E145"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
